--- a/03_内部設計/022-クラス仕様書/servlet/SearchResultServletのクラス仕様書.xlsx
+++ b/03_内部設計/022-クラス仕様書/servlet/SearchResultServletのクラス仕様書.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB5BF018-1A9B-4193-B2F0-683BF96C5626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B661FE1D-687D-46F2-BEEC-060067687286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="クラス仕様" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（doGet）'!$A$1:$BI$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'メソッド仕様（doPost）'!$A$1:$BI$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'メソッド仕様（doPost）'!$A$1:$BI$58</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="107">
   <si>
     <t>クラス仕様書</t>
   </si>
@@ -251,10 +251,6 @@
     <rPh sb="3" eb="11">
       <t>ショウヒンケンサクケッカガメン</t>
     </rPh>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>request, response</t>
     <phoneticPr fontId="7"/>
   </si>
   <si>
@@ -496,10 +492,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>8) エラーメッセージをリクエストオブジェクトから削除する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>WebServletアノテーションの引数は、自身のクラス名にすること。
 doGet: 商品検索結果画面(search_result.jsp)に検索結果を表示する。10件ごとのページング処理を行う。
 doPost: 検索キーワードと商品カテゴリーIDから、商品検索を行う。</t>
@@ -687,22 +679,6 @@
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>8.1) ServletRequestクラスのremoveAttributeメソッドを呼び出し、引数に"error"を代入する。</t>
-    <rPh sb="43" eb="44">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="45" eb="46">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ヒキスウ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>ダイニュウ</t>
-    </rPh>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
     <t>5.2.1) if文で条件分岐処理を行う。</t>
     <rPh sb="9" eb="10">
       <t>ブン</t>
@@ -782,6 +758,13 @@
       <t>ワタ</t>
     </rPh>
     <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>request</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>request, response</t>
   </si>
 </sst>
 </file>
@@ -995,7 +978,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1089,29 +1072,29 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1133,6 +1116,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1499,71 +1488,71 @@
       <c r="J1" s="35"/>
       <c r="K1" s="35"/>
       <c r="L1" s="35"/>
-      <c r="M1" s="31" t="s">
+      <c r="M1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="32" t="s">
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="31" t="s">
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="31"/>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="32" t="s">
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="31" t="s">
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="36"/>
+      <c r="AH1" s="36"/>
+      <c r="AI1" s="36"/>
+      <c r="AJ1" s="36"/>
+      <c r="AK1" s="36"/>
+      <c r="AL1" s="36"/>
+      <c r="AM1" s="36"/>
+      <c r="AN1" s="36"/>
+      <c r="AO1" s="36"/>
+      <c r="AP1" s="36"/>
+      <c r="AQ1" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="AR1" s="31"/>
-      <c r="AS1" s="31"/>
-      <c r="AT1" s="32" t="s">
+      <c r="AR1" s="37"/>
+      <c r="AS1" s="37"/>
+      <c r="AT1" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="AU1" s="32"/>
-      <c r="AV1" s="32"/>
-      <c r="AW1" s="32"/>
-      <c r="AX1" s="32"/>
-      <c r="AY1" s="32"/>
-      <c r="AZ1" s="32"/>
-      <c r="BA1" s="31" t="s">
+      <c r="AU1" s="36"/>
+      <c r="AV1" s="36"/>
+      <c r="AW1" s="36"/>
+      <c r="AX1" s="36"/>
+      <c r="AY1" s="36"/>
+      <c r="AZ1" s="36"/>
+      <c r="BA1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="BB1" s="31"/>
-      <c r="BC1" s="31"/>
-      <c r="BD1" s="33">
+      <c r="BB1" s="37"/>
+      <c r="BC1" s="37"/>
+      <c r="BD1" s="34">
         <v>45566</v>
       </c>
-      <c r="BE1" s="33"/>
-      <c r="BF1" s="33"/>
-      <c r="BG1" s="33"/>
-      <c r="BH1" s="33"/>
-      <c r="BI1" s="33"/>
+      <c r="BE1" s="34"/>
+      <c r="BF1" s="34"/>
+      <c r="BG1" s="34"/>
+      <c r="BH1" s="34"/>
+      <c r="BI1" s="34"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -1775,70 +1764,70 @@
       <c r="J2" s="35"/>
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
-      <c r="M2" s="31" t="s">
+      <c r="M2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="36"/>
-      <c r="AA2" s="36"/>
-      <c r="AB2" s="31" t="s">
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="31"/>
-      <c r="AD2" s="31"/>
-      <c r="AE2" s="32" t="str">
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="37"/>
+      <c r="AE2" s="36" t="str">
         <f>クラス仕様!G5</f>
         <v>SearchResultServlet</v>
       </c>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="32"/>
-      <c r="AN2" s="32"/>
-      <c r="AO2" s="32"/>
-      <c r="AP2" s="32"/>
-      <c r="AQ2" s="31" t="s">
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
+      <c r="AJ2" s="36"/>
+      <c r="AK2" s="36"/>
+      <c r="AL2" s="36"/>
+      <c r="AM2" s="36"/>
+      <c r="AN2" s="36"/>
+      <c r="AO2" s="36"/>
+      <c r="AP2" s="36"/>
+      <c r="AQ2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="AR2" s="31"/>
-      <c r="AS2" s="31"/>
-      <c r="AT2" s="32" t="s">
+      <c r="AR2" s="37"/>
+      <c r="AS2" s="37"/>
+      <c r="AT2" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="AU2" s="32"/>
-      <c r="AV2" s="32"/>
-      <c r="AW2" s="32"/>
-      <c r="AX2" s="32"/>
-      <c r="AY2" s="32"/>
-      <c r="AZ2" s="32"/>
-      <c r="BA2" s="31" t="s">
+      <c r="AU2" s="36"/>
+      <c r="AV2" s="36"/>
+      <c r="AW2" s="36"/>
+      <c r="AX2" s="36"/>
+      <c r="AY2" s="36"/>
+      <c r="AZ2" s="36"/>
+      <c r="BA2" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="BB2" s="31"/>
-      <c r="BC2" s="31"/>
-      <c r="BD2" s="33">
+      <c r="BB2" s="37"/>
+      <c r="BC2" s="37"/>
+      <c r="BD2" s="34">
         <v>45568</v>
       </c>
-      <c r="BE2" s="33"/>
-      <c r="BF2" s="33"/>
-      <c r="BG2" s="33"/>
-      <c r="BH2" s="33"/>
-      <c r="BI2" s="33"/>
+      <c r="BE2" s="34"/>
+      <c r="BF2" s="34"/>
+      <c r="BG2" s="34"/>
+      <c r="BH2" s="34"/>
+      <c r="BI2" s="34"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -2038,1116 +2027,1146 @@
       <c r="IX2" s="1"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="38" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="38"/>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="38"/>
-      <c r="AM4" s="38"/>
-      <c r="AN4" s="38"/>
-      <c r="AO4" s="38"/>
-      <c r="AP4" s="38"/>
-      <c r="AQ4" s="38"/>
-      <c r="AR4" s="38"/>
-      <c r="AS4" s="38"/>
-      <c r="AT4" s="38"/>
-      <c r="AU4" s="38"/>
-      <c r="AV4" s="38"/>
-      <c r="AW4" s="38"/>
-      <c r="AX4" s="38"/>
-      <c r="AY4" s="38"/>
-      <c r="AZ4" s="38"/>
-      <c r="BA4" s="38"/>
-      <c r="BB4" s="38"/>
-      <c r="BC4" s="38"/>
-      <c r="BD4" s="38"/>
-      <c r="BE4" s="38"/>
-      <c r="BF4" s="38"/>
-      <c r="BG4" s="38"/>
-      <c r="BH4" s="38"/>
-      <c r="BI4" s="38"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="32"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="32"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="32"/>
+      <c r="AA4" s="32"/>
+      <c r="AB4" s="32"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="32"/>
+      <c r="AE4" s="32"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="32"/>
+      <c r="AH4" s="32"/>
+      <c r="AI4" s="32"/>
+      <c r="AJ4" s="32"/>
+      <c r="AK4" s="32"/>
+      <c r="AL4" s="32"/>
+      <c r="AM4" s="32"/>
+      <c r="AN4" s="32"/>
+      <c r="AO4" s="32"/>
+      <c r="AP4" s="32"/>
+      <c r="AQ4" s="32"/>
+      <c r="AR4" s="32"/>
+      <c r="AS4" s="32"/>
+      <c r="AT4" s="32"/>
+      <c r="AU4" s="32"/>
+      <c r="AV4" s="32"/>
+      <c r="AW4" s="32"/>
+      <c r="AX4" s="32"/>
+      <c r="AY4" s="32"/>
+      <c r="AZ4" s="32"/>
+      <c r="BA4" s="32"/>
+      <c r="BB4" s="32"/>
+      <c r="BC4" s="32"/>
+      <c r="BD4" s="32"/>
+      <c r="BE4" s="32"/>
+      <c r="BF4" s="32"/>
+      <c r="BG4" s="32"/>
+      <c r="BH4" s="32"/>
+      <c r="BI4" s="32"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="38" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="38"/>
-      <c r="Y5" s="38"/>
-      <c r="Z5" s="38"/>
-      <c r="AA5" s="38"/>
-      <c r="AB5" s="38"/>
-      <c r="AC5" s="38"/>
-      <c r="AD5" s="38"/>
-      <c r="AE5" s="38"/>
-      <c r="AF5" s="38"/>
-      <c r="AG5" s="38"/>
-      <c r="AH5" s="38"/>
-      <c r="AI5" s="38"/>
-      <c r="AJ5" s="38"/>
-      <c r="AK5" s="38"/>
-      <c r="AL5" s="38"/>
-      <c r="AM5" s="38"/>
-      <c r="AN5" s="38"/>
-      <c r="AO5" s="38"/>
-      <c r="AP5" s="38"/>
-      <c r="AQ5" s="38"/>
-      <c r="AR5" s="38"/>
-      <c r="AS5" s="38"/>
-      <c r="AT5" s="38"/>
-      <c r="AU5" s="38"/>
-      <c r="AV5" s="38"/>
-      <c r="AW5" s="38"/>
-      <c r="AX5" s="38"/>
-      <c r="AY5" s="38"/>
-      <c r="AZ5" s="38"/>
-      <c r="BA5" s="38"/>
-      <c r="BB5" s="38"/>
-      <c r="BC5" s="38"/>
-      <c r="BD5" s="38"/>
-      <c r="BE5" s="38"/>
-      <c r="BF5" s="38"/>
-      <c r="BG5" s="38"/>
-      <c r="BH5" s="38"/>
-      <c r="BI5" s="38"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="32"/>
+      <c r="S5" s="32"/>
+      <c r="T5" s="32"/>
+      <c r="U5" s="32"/>
+      <c r="V5" s="32"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="32"/>
+      <c r="Z5" s="32"/>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="32"/>
+      <c r="AC5" s="32"/>
+      <c r="AD5" s="32"/>
+      <c r="AE5" s="32"/>
+      <c r="AF5" s="32"/>
+      <c r="AG5" s="32"/>
+      <c r="AH5" s="32"/>
+      <c r="AI5" s="32"/>
+      <c r="AJ5" s="32"/>
+      <c r="AK5" s="32"/>
+      <c r="AL5" s="32"/>
+      <c r="AM5" s="32"/>
+      <c r="AN5" s="32"/>
+      <c r="AO5" s="32"/>
+      <c r="AP5" s="32"/>
+      <c r="AQ5" s="32"/>
+      <c r="AR5" s="32"/>
+      <c r="AS5" s="32"/>
+      <c r="AT5" s="32"/>
+      <c r="AU5" s="32"/>
+      <c r="AV5" s="32"/>
+      <c r="AW5" s="32"/>
+      <c r="AX5" s="32"/>
+      <c r="AY5" s="32"/>
+      <c r="AZ5" s="32"/>
+      <c r="BA5" s="32"/>
+      <c r="BB5" s="32"/>
+      <c r="BC5" s="32"/>
+      <c r="BD5" s="32"/>
+      <c r="BE5" s="32"/>
+      <c r="BF5" s="32"/>
+      <c r="BG5" s="32"/>
+      <c r="BH5" s="32"/>
+      <c r="BI5" s="32"/>
     </row>
     <row r="6" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="38" t="s">
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="38"/>
-      <c r="T6" s="38"/>
-      <c r="U6" s="38"/>
-      <c r="V6" s="38"/>
-      <c r="W6" s="38"/>
-      <c r="X6" s="38"/>
-      <c r="Y6" s="38"/>
-      <c r="Z6" s="38"/>
-      <c r="AA6" s="38"/>
-      <c r="AB6" s="38"/>
-      <c r="AC6" s="38"/>
-      <c r="AD6" s="37" t="s">
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="32"/>
+      <c r="S6" s="32"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="32"/>
+      <c r="W6" s="32"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="32"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="AE6" s="37"/>
-      <c r="AF6" s="37"/>
-      <c r="AG6" s="37"/>
-      <c r="AH6" s="37"/>
-      <c r="AI6" s="37"/>
-      <c r="AJ6" s="38" t="s">
+      <c r="AE6" s="33"/>
+      <c r="AF6" s="33"/>
+      <c r="AG6" s="33"/>
+      <c r="AH6" s="33"/>
+      <c r="AI6" s="33"/>
+      <c r="AJ6" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="AK6" s="38"/>
-      <c r="AL6" s="38"/>
-      <c r="AM6" s="38"/>
-      <c r="AN6" s="38"/>
-      <c r="AO6" s="38"/>
-      <c r="AP6" s="38"/>
-      <c r="AQ6" s="38"/>
-      <c r="AR6" s="38"/>
-      <c r="AS6" s="38"/>
-      <c r="AT6" s="38"/>
-      <c r="AU6" s="38"/>
-      <c r="AV6" s="38"/>
-      <c r="AW6" s="38"/>
-      <c r="AX6" s="38"/>
-      <c r="AY6" s="38"/>
-      <c r="AZ6" s="38"/>
-      <c r="BA6" s="38"/>
-      <c r="BB6" s="38"/>
-      <c r="BC6" s="38"/>
-      <c r="BD6" s="38"/>
-      <c r="BE6" s="38"/>
-      <c r="BF6" s="38"/>
-      <c r="BG6" s="38"/>
-      <c r="BH6" s="38"/>
-      <c r="BI6" s="38"/>
+      <c r="AK6" s="32"/>
+      <c r="AL6" s="32"/>
+      <c r="AM6" s="32"/>
+      <c r="AN6" s="32"/>
+      <c r="AO6" s="32"/>
+      <c r="AP6" s="32"/>
+      <c r="AQ6" s="32"/>
+      <c r="AR6" s="32"/>
+      <c r="AS6" s="32"/>
+      <c r="AT6" s="32"/>
+      <c r="AU6" s="32"/>
+      <c r="AV6" s="32"/>
+      <c r="AW6" s="32"/>
+      <c r="AX6" s="32"/>
+      <c r="AY6" s="32"/>
+      <c r="AZ6" s="32"/>
+      <c r="BA6" s="32"/>
+      <c r="BB6" s="32"/>
+      <c r="BC6" s="32"/>
+      <c r="BD6" s="32"/>
+      <c r="BE6" s="32"/>
+      <c r="BF6" s="32"/>
+      <c r="BG6" s="32"/>
+      <c r="BH6" s="32"/>
+      <c r="BI6" s="32"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37" t="s">
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="37" t="s">
+      <c r="L8" s="33"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="V8" s="37"/>
-      <c r="W8" s="37"/>
-      <c r="X8" s="37"/>
-      <c r="Y8" s="37"/>
-      <c r="Z8" s="37"/>
-      <c r="AA8" s="37"/>
-      <c r="AB8" s="37"/>
-      <c r="AC8" s="37"/>
-      <c r="AD8" s="37"/>
-      <c r="AE8" s="37" t="s">
+      <c r="V8" s="33"/>
+      <c r="W8" s="33"/>
+      <c r="X8" s="33"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="33"/>
+      <c r="AA8" s="33"/>
+      <c r="AB8" s="33"/>
+      <c r="AC8" s="33"/>
+      <c r="AD8" s="33"/>
+      <c r="AE8" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="AF8" s="37"/>
-      <c r="AG8" s="37"/>
-      <c r="AH8" s="37"/>
-      <c r="AI8" s="37"/>
-      <c r="AJ8" s="37"/>
-      <c r="AK8" s="37"/>
-      <c r="AL8" s="37"/>
-      <c r="AM8" s="37"/>
-      <c r="AN8" s="37"/>
-      <c r="AO8" s="37" t="s">
+      <c r="AF8" s="33"/>
+      <c r="AG8" s="33"/>
+      <c r="AH8" s="33"/>
+      <c r="AI8" s="33"/>
+      <c r="AJ8" s="33"/>
+      <c r="AK8" s="33"/>
+      <c r="AL8" s="33"/>
+      <c r="AM8" s="33"/>
+      <c r="AN8" s="33"/>
+      <c r="AO8" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="AP8" s="37"/>
-      <c r="AQ8" s="37"/>
-      <c r="AR8" s="37"/>
-      <c r="AS8" s="37"/>
-      <c r="AT8" s="37"/>
-      <c r="AU8" s="37"/>
-      <c r="AV8" s="37"/>
-      <c r="AW8" s="37"/>
-      <c r="AX8" s="37"/>
-      <c r="AY8" s="37"/>
-      <c r="AZ8" s="37"/>
-      <c r="BA8" s="37"/>
-      <c r="BB8" s="37"/>
-      <c r="BC8" s="37"/>
-      <c r="BD8" s="37"/>
-      <c r="BE8" s="37"/>
-      <c r="BF8" s="37"/>
-      <c r="BG8" s="37"/>
-      <c r="BH8" s="37"/>
-      <c r="BI8" s="37"/>
+      <c r="AP8" s="33"/>
+      <c r="AQ8" s="33"/>
+      <c r="AR8" s="33"/>
+      <c r="AS8" s="33"/>
+      <c r="AT8" s="33"/>
+      <c r="AU8" s="33"/>
+      <c r="AV8" s="33"/>
+      <c r="AW8" s="33"/>
+      <c r="AX8" s="33"/>
+      <c r="AY8" s="33"/>
+      <c r="AZ8" s="33"/>
+      <c r="BA8" s="33"/>
+      <c r="BB8" s="33"/>
+      <c r="BC8" s="33"/>
+      <c r="BD8" s="33"/>
+      <c r="BE8" s="33"/>
+      <c r="BF8" s="33"/>
+      <c r="BG8" s="33"/>
+      <c r="BH8" s="33"/>
+      <c r="BI8" s="33"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="34"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="34"/>
-      <c r="T9" s="34"/>
-      <c r="U9" s="34"/>
-      <c r="V9" s="34"/>
-      <c r="W9" s="34"/>
-      <c r="X9" s="34"/>
-      <c r="Y9" s="34"/>
-      <c r="Z9" s="34"/>
-      <c r="AA9" s="34"/>
-      <c r="AB9" s="34"/>
-      <c r="AC9" s="34"/>
-      <c r="AD9" s="34"/>
-      <c r="AE9" s="34"/>
-      <c r="AF9" s="34"/>
-      <c r="AG9" s="34"/>
-      <c r="AH9" s="34"/>
-      <c r="AI9" s="34"/>
-      <c r="AJ9" s="34"/>
-      <c r="AK9" s="34"/>
-      <c r="AL9" s="34"/>
-      <c r="AM9" s="34"/>
-      <c r="AN9" s="34"/>
-      <c r="AO9" s="34"/>
-      <c r="AP9" s="34"/>
-      <c r="AQ9" s="34"/>
-      <c r="AR9" s="34"/>
-      <c r="AS9" s="34"/>
-      <c r="AT9" s="34"/>
-      <c r="AU9" s="34"/>
-      <c r="AV9" s="34"/>
-      <c r="AW9" s="34"/>
-      <c r="AX9" s="34"/>
-      <c r="AY9" s="34"/>
-      <c r="AZ9" s="34"/>
-      <c r="BA9" s="34"/>
-      <c r="BB9" s="34"/>
-      <c r="BC9" s="34"/>
-      <c r="BD9" s="34"/>
-      <c r="BE9" s="34"/>
-      <c r="BF9" s="34"/>
-      <c r="BG9" s="34"/>
-      <c r="BH9" s="34"/>
-      <c r="BI9" s="34"/>
+      <c r="A9" s="31"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="31"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="31"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="31"/>
+      <c r="AB9" s="31"/>
+      <c r="AC9" s="31"/>
+      <c r="AD9" s="31"/>
+      <c r="AE9" s="31"/>
+      <c r="AF9" s="31"/>
+      <c r="AG9" s="31"/>
+      <c r="AH9" s="31"/>
+      <c r="AI9" s="31"/>
+      <c r="AJ9" s="31"/>
+      <c r="AK9" s="31"/>
+      <c r="AL9" s="31"/>
+      <c r="AM9" s="31"/>
+      <c r="AN9" s="31"/>
+      <c r="AO9" s="31"/>
+      <c r="AP9" s="31"/>
+      <c r="AQ9" s="31"/>
+      <c r="AR9" s="31"/>
+      <c r="AS9" s="31"/>
+      <c r="AT9" s="31"/>
+      <c r="AU9" s="31"/>
+      <c r="AV9" s="31"/>
+      <c r="AW9" s="31"/>
+      <c r="AX9" s="31"/>
+      <c r="AY9" s="31"/>
+      <c r="AZ9" s="31"/>
+      <c r="BA9" s="31"/>
+      <c r="BB9" s="31"/>
+      <c r="BC9" s="31"/>
+      <c r="BD9" s="31"/>
+      <c r="BE9" s="31"/>
+      <c r="BF9" s="31"/>
+      <c r="BG9" s="31"/>
+      <c r="BH9" s="31"/>
+      <c r="BI9" s="31"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="34"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="34"/>
-      <c r="P10" s="34"/>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="34"/>
-      <c r="S10" s="34"/>
-      <c r="T10" s="34"/>
-      <c r="U10" s="34"/>
-      <c r="V10" s="34"/>
-      <c r="W10" s="34"/>
-      <c r="X10" s="34"/>
-      <c r="Y10" s="34"/>
-      <c r="Z10" s="34"/>
-      <c r="AA10" s="34"/>
-      <c r="AB10" s="34"/>
-      <c r="AC10" s="34"/>
-      <c r="AD10" s="34"/>
-      <c r="AE10" s="34"/>
-      <c r="AF10" s="34"/>
-      <c r="AG10" s="34"/>
-      <c r="AH10" s="34"/>
-      <c r="AI10" s="34"/>
-      <c r="AJ10" s="34"/>
-      <c r="AK10" s="34"/>
-      <c r="AL10" s="34"/>
-      <c r="AM10" s="34"/>
-      <c r="AN10" s="34"/>
-      <c r="AO10" s="34"/>
-      <c r="AP10" s="34"/>
-      <c r="AQ10" s="34"/>
-      <c r="AR10" s="34"/>
-      <c r="AS10" s="34"/>
-      <c r="AT10" s="34"/>
-      <c r="AU10" s="34"/>
-      <c r="AV10" s="34"/>
-      <c r="AW10" s="34"/>
-      <c r="AX10" s="34"/>
-      <c r="AY10" s="34"/>
-      <c r="AZ10" s="34"/>
-      <c r="BA10" s="34"/>
-      <c r="BB10" s="34"/>
-      <c r="BC10" s="34"/>
-      <c r="BD10" s="34"/>
-      <c r="BE10" s="34"/>
-      <c r="BF10" s="34"/>
-      <c r="BG10" s="34"/>
-      <c r="BH10" s="34"/>
-      <c r="BI10" s="34"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="31"/>
+      <c r="Y10" s="31"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="31"/>
+      <c r="AB10" s="31"/>
+      <c r="AC10" s="31"/>
+      <c r="AD10" s="31"/>
+      <c r="AE10" s="31"/>
+      <c r="AF10" s="31"/>
+      <c r="AG10" s="31"/>
+      <c r="AH10" s="31"/>
+      <c r="AI10" s="31"/>
+      <c r="AJ10" s="31"/>
+      <c r="AK10" s="31"/>
+      <c r="AL10" s="31"/>
+      <c r="AM10" s="31"/>
+      <c r="AN10" s="31"/>
+      <c r="AO10" s="31"/>
+      <c r="AP10" s="31"/>
+      <c r="AQ10" s="31"/>
+      <c r="AR10" s="31"/>
+      <c r="AS10" s="31"/>
+      <c r="AT10" s="31"/>
+      <c r="AU10" s="31"/>
+      <c r="AV10" s="31"/>
+      <c r="AW10" s="31"/>
+      <c r="AX10" s="31"/>
+      <c r="AY10" s="31"/>
+      <c r="AZ10" s="31"/>
+      <c r="BA10" s="31"/>
+      <c r="BB10" s="31"/>
+      <c r="BC10" s="31"/>
+      <c r="BD10" s="31"/>
+      <c r="BE10" s="31"/>
+      <c r="BF10" s="31"/>
+      <c r="BG10" s="31"/>
+      <c r="BH10" s="31"/>
+      <c r="BI10" s="31"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="34"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="34"/>
-      <c r="S11" s="34"/>
-      <c r="T11" s="34"/>
-      <c r="U11" s="34"/>
-      <c r="V11" s="34"/>
-      <c r="W11" s="34"/>
-      <c r="X11" s="34"/>
-      <c r="Y11" s="34"/>
-      <c r="Z11" s="34"/>
-      <c r="AA11" s="34"/>
-      <c r="AB11" s="34"/>
-      <c r="AC11" s="34"/>
-      <c r="AD11" s="34"/>
-      <c r="AE11" s="34"/>
-      <c r="AF11" s="34"/>
-      <c r="AG11" s="34"/>
-      <c r="AH11" s="34"/>
-      <c r="AI11" s="34"/>
-      <c r="AJ11" s="34"/>
-      <c r="AK11" s="34"/>
-      <c r="AL11" s="34"/>
-      <c r="AM11" s="34"/>
-      <c r="AN11" s="34"/>
-      <c r="AO11" s="34"/>
-      <c r="AP11" s="34"/>
-      <c r="AQ11" s="34"/>
-      <c r="AR11" s="34"/>
-      <c r="AS11" s="34"/>
-      <c r="AT11" s="34"/>
-      <c r="AU11" s="34"/>
-      <c r="AV11" s="34"/>
-      <c r="AW11" s="34"/>
-      <c r="AX11" s="34"/>
-      <c r="AY11" s="34"/>
-      <c r="AZ11" s="34"/>
-      <c r="BA11" s="34"/>
-      <c r="BB11" s="34"/>
-      <c r="BC11" s="34"/>
-      <c r="BD11" s="34"/>
-      <c r="BE11" s="34"/>
-      <c r="BF11" s="34"/>
-      <c r="BG11" s="34"/>
-      <c r="BH11" s="34"/>
-      <c r="BI11" s="34"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="31"/>
+      <c r="AB11" s="31"/>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="31"/>
+      <c r="AE11" s="31"/>
+      <c r="AF11" s="31"/>
+      <c r="AG11" s="31"/>
+      <c r="AH11" s="31"/>
+      <c r="AI11" s="31"/>
+      <c r="AJ11" s="31"/>
+      <c r="AK11" s="31"/>
+      <c r="AL11" s="31"/>
+      <c r="AM11" s="31"/>
+      <c r="AN11" s="31"/>
+      <c r="AO11" s="31"/>
+      <c r="AP11" s="31"/>
+      <c r="AQ11" s="31"/>
+      <c r="AR11" s="31"/>
+      <c r="AS11" s="31"/>
+      <c r="AT11" s="31"/>
+      <c r="AU11" s="31"/>
+      <c r="AV11" s="31"/>
+      <c r="AW11" s="31"/>
+      <c r="AX11" s="31"/>
+      <c r="AY11" s="31"/>
+      <c r="AZ11" s="31"/>
+      <c r="BA11" s="31"/>
+      <c r="BB11" s="31"/>
+      <c r="BC11" s="31"/>
+      <c r="BD11" s="31"/>
+      <c r="BE11" s="31"/>
+      <c r="BF11" s="31"/>
+      <c r="BG11" s="31"/>
+      <c r="BH11" s="31"/>
+      <c r="BI11" s="31"/>
     </row>
     <row r="12" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="34"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="34"/>
-      <c r="V12" s="34"/>
-      <c r="W12" s="34"/>
-      <c r="X12" s="34"/>
-      <c r="Y12" s="34"/>
-      <c r="Z12" s="34"/>
-      <c r="AA12" s="34"/>
-      <c r="AB12" s="34"/>
-      <c r="AC12" s="34"/>
-      <c r="AD12" s="34"/>
-      <c r="AE12" s="34"/>
-      <c r="AF12" s="34"/>
-      <c r="AG12" s="34"/>
-      <c r="AH12" s="34"/>
-      <c r="AI12" s="34"/>
-      <c r="AJ12" s="34"/>
-      <c r="AK12" s="34"/>
-      <c r="AL12" s="34"/>
-      <c r="AM12" s="34"/>
-      <c r="AN12" s="34"/>
-      <c r="AO12" s="34"/>
-      <c r="AP12" s="34"/>
-      <c r="AQ12" s="34"/>
-      <c r="AR12" s="34"/>
-      <c r="AS12" s="34"/>
-      <c r="AT12" s="34"/>
-      <c r="AU12" s="34"/>
-      <c r="AV12" s="34"/>
-      <c r="AW12" s="34"/>
-      <c r="AX12" s="34"/>
-      <c r="AY12" s="34"/>
-      <c r="AZ12" s="34"/>
-      <c r="BA12" s="34"/>
-      <c r="BB12" s="34"/>
-      <c r="BC12" s="34"/>
-      <c r="BD12" s="34"/>
-      <c r="BE12" s="34"/>
-      <c r="BF12" s="34"/>
-      <c r="BG12" s="34"/>
-      <c r="BH12" s="34"/>
-      <c r="BI12" s="34"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="31"/>
+      <c r="V12" s="31"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="31"/>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="31"/>
+      <c r="AE12" s="31"/>
+      <c r="AF12" s="31"/>
+      <c r="AG12" s="31"/>
+      <c r="AH12" s="31"/>
+      <c r="AI12" s="31"/>
+      <c r="AJ12" s="31"/>
+      <c r="AK12" s="31"/>
+      <c r="AL12" s="31"/>
+      <c r="AM12" s="31"/>
+      <c r="AN12" s="31"/>
+      <c r="AO12" s="31"/>
+      <c r="AP12" s="31"/>
+      <c r="AQ12" s="31"/>
+      <c r="AR12" s="31"/>
+      <c r="AS12" s="31"/>
+      <c r="AT12" s="31"/>
+      <c r="AU12" s="31"/>
+      <c r="AV12" s="31"/>
+      <c r="AW12" s="31"/>
+      <c r="AX12" s="31"/>
+      <c r="AY12" s="31"/>
+      <c r="AZ12" s="31"/>
+      <c r="BA12" s="31"/>
+      <c r="BB12" s="31"/>
+      <c r="BC12" s="31"/>
+      <c r="BD12" s="31"/>
+      <c r="BE12" s="31"/>
+      <c r="BF12" s="31"/>
+      <c r="BG12" s="31"/>
+      <c r="BH12" s="31"/>
+      <c r="BI12" s="31"/>
     </row>
     <row r="13" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-      <c r="U13" s="34"/>
-      <c r="V13" s="34"/>
-      <c r="W13" s="34"/>
-      <c r="X13" s="34"/>
-      <c r="Y13" s="34"/>
-      <c r="Z13" s="34"/>
-      <c r="AA13" s="34"/>
-      <c r="AB13" s="34"/>
-      <c r="AC13" s="34"/>
-      <c r="AD13" s="34"/>
-      <c r="AE13" s="34"/>
-      <c r="AF13" s="34"/>
-      <c r="AG13" s="34"/>
-      <c r="AH13" s="34"/>
-      <c r="AI13" s="34"/>
-      <c r="AJ13" s="34"/>
-      <c r="AK13" s="34"/>
-      <c r="AL13" s="34"/>
-      <c r="AM13" s="34"/>
-      <c r="AN13" s="34"/>
-      <c r="AO13" s="34"/>
-      <c r="AP13" s="34"/>
-      <c r="AQ13" s="34"/>
-      <c r="AR13" s="34"/>
-      <c r="AS13" s="34"/>
-      <c r="AT13" s="34"/>
-      <c r="AU13" s="34"/>
-      <c r="AV13" s="34"/>
-      <c r="AW13" s="34"/>
-      <c r="AX13" s="34"/>
-      <c r="AY13" s="34"/>
-      <c r="AZ13" s="34"/>
-      <c r="BA13" s="34"/>
-      <c r="BB13" s="34"/>
-      <c r="BC13" s="34"/>
-      <c r="BD13" s="34"/>
-      <c r="BE13" s="34"/>
-      <c r="BF13" s="34"/>
-      <c r="BG13" s="34"/>
-      <c r="BH13" s="34"/>
-      <c r="BI13" s="34"/>
+      <c r="A13" s="31"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="31"/>
+      <c r="V13" s="31"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="31"/>
+      <c r="Y13" s="31"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="31"/>
+      <c r="AB13" s="31"/>
+      <c r="AC13" s="31"/>
+      <c r="AD13" s="31"/>
+      <c r="AE13" s="31"/>
+      <c r="AF13" s="31"/>
+      <c r="AG13" s="31"/>
+      <c r="AH13" s="31"/>
+      <c r="AI13" s="31"/>
+      <c r="AJ13" s="31"/>
+      <c r="AK13" s="31"/>
+      <c r="AL13" s="31"/>
+      <c r="AM13" s="31"/>
+      <c r="AN13" s="31"/>
+      <c r="AO13" s="31"/>
+      <c r="AP13" s="31"/>
+      <c r="AQ13" s="31"/>
+      <c r="AR13" s="31"/>
+      <c r="AS13" s="31"/>
+      <c r="AT13" s="31"/>
+      <c r="AU13" s="31"/>
+      <c r="AV13" s="31"/>
+      <c r="AW13" s="31"/>
+      <c r="AX13" s="31"/>
+      <c r="AY13" s="31"/>
+      <c r="AZ13" s="31"/>
+      <c r="BA13" s="31"/>
+      <c r="BB13" s="31"/>
+      <c r="BC13" s="31"/>
+      <c r="BD13" s="31"/>
+      <c r="BE13" s="31"/>
+      <c r="BF13" s="31"/>
+      <c r="BG13" s="31"/>
+      <c r="BH13" s="31"/>
+      <c r="BI13" s="31"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="34"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="34"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="34"/>
-      <c r="U14" s="34"/>
-      <c r="V14" s="34"/>
-      <c r="W14" s="34"/>
-      <c r="X14" s="34"/>
-      <c r="Y14" s="34"/>
-      <c r="Z14" s="34"/>
-      <c r="AA14" s="34"/>
-      <c r="AB14" s="34"/>
-      <c r="AC14" s="34"/>
-      <c r="AD14" s="34"/>
-      <c r="AE14" s="34"/>
-      <c r="AF14" s="34"/>
-      <c r="AG14" s="34"/>
-      <c r="AH14" s="34"/>
-      <c r="AI14" s="34"/>
-      <c r="AJ14" s="34"/>
-      <c r="AK14" s="34"/>
-      <c r="AL14" s="34"/>
-      <c r="AM14" s="34"/>
-      <c r="AN14" s="34"/>
-      <c r="AO14" s="34"/>
-      <c r="AP14" s="34"/>
-      <c r="AQ14" s="34"/>
-      <c r="AR14" s="34"/>
-      <c r="AS14" s="34"/>
-      <c r="AT14" s="34"/>
-      <c r="AU14" s="34"/>
-      <c r="AV14" s="34"/>
-      <c r="AW14" s="34"/>
-      <c r="AX14" s="34"/>
-      <c r="AY14" s="34"/>
-      <c r="AZ14" s="34"/>
-      <c r="BA14" s="34"/>
-      <c r="BB14" s="34"/>
-      <c r="BC14" s="34"/>
-      <c r="BD14" s="34"/>
-      <c r="BE14" s="34"/>
-      <c r="BF14" s="34"/>
-      <c r="BG14" s="34"/>
-      <c r="BH14" s="34"/>
-      <c r="BI14" s="34"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
+      <c r="P14" s="31"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="31"/>
+      <c r="V14" s="31"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="31"/>
+      <c r="Y14" s="31"/>
+      <c r="Z14" s="31"/>
+      <c r="AA14" s="31"/>
+      <c r="AB14" s="31"/>
+      <c r="AC14" s="31"/>
+      <c r="AD14" s="31"/>
+      <c r="AE14" s="31"/>
+      <c r="AF14" s="31"/>
+      <c r="AG14" s="31"/>
+      <c r="AH14" s="31"/>
+      <c r="AI14" s="31"/>
+      <c r="AJ14" s="31"/>
+      <c r="AK14" s="31"/>
+      <c r="AL14" s="31"/>
+      <c r="AM14" s="31"/>
+      <c r="AN14" s="31"/>
+      <c r="AO14" s="31"/>
+      <c r="AP14" s="31"/>
+      <c r="AQ14" s="31"/>
+      <c r="AR14" s="31"/>
+      <c r="AS14" s="31"/>
+      <c r="AT14" s="31"/>
+      <c r="AU14" s="31"/>
+      <c r="AV14" s="31"/>
+      <c r="AW14" s="31"/>
+      <c r="AX14" s="31"/>
+      <c r="AY14" s="31"/>
+      <c r="AZ14" s="31"/>
+      <c r="BA14" s="31"/>
+      <c r="BB14" s="31"/>
+      <c r="BC14" s="31"/>
+      <c r="BD14" s="31"/>
+      <c r="BE14" s="31"/>
+      <c r="BF14" s="31"/>
+      <c r="BG14" s="31"/>
+      <c r="BH14" s="31"/>
+      <c r="BI14" s="31"/>
     </row>
     <row r="16" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
-      <c r="L16" s="37"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
-      <c r="S16" s="37"/>
-      <c r="T16" s="37"/>
-      <c r="U16" s="37"/>
-      <c r="V16" s="37"/>
-      <c r="W16" s="37"/>
-      <c r="X16" s="37"/>
-      <c r="Y16" s="37"/>
-      <c r="Z16" s="37"/>
-      <c r="AA16" s="37"/>
-      <c r="AB16" s="37"/>
-      <c r="AC16" s="37"/>
-      <c r="AD16" s="37"/>
-      <c r="AE16" s="37"/>
-      <c r="AF16" s="37"/>
-      <c r="AG16" s="37"/>
-      <c r="AH16" s="37"/>
-      <c r="AI16" s="37"/>
-      <c r="AJ16" s="37"/>
-      <c r="AK16" s="37"/>
-      <c r="AL16" s="37"/>
-      <c r="AM16" s="37"/>
-      <c r="AN16" s="37"/>
-      <c r="AO16" s="37"/>
-      <c r="AP16" s="37"/>
-      <c r="AQ16" s="37"/>
-      <c r="AR16" s="37"/>
-      <c r="AS16" s="37"/>
-      <c r="AT16" s="37"/>
-      <c r="AU16" s="37"/>
-      <c r="AV16" s="37"/>
-      <c r="AW16" s="37"/>
-      <c r="AX16" s="37"/>
-      <c r="AY16" s="37"/>
-      <c r="AZ16" s="37"/>
-      <c r="BA16" s="37"/>
-      <c r="BB16" s="37"/>
-      <c r="BC16" s="37"/>
-      <c r="BD16" s="37"/>
-      <c r="BE16" s="37"/>
-      <c r="BF16" s="37"/>
-      <c r="BG16" s="37"/>
-      <c r="BH16" s="37"/>
-      <c r="BI16" s="37"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="33"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="33"/>
+      <c r="Y16" s="33"/>
+      <c r="Z16" s="33"/>
+      <c r="AA16" s="33"/>
+      <c r="AB16" s="33"/>
+      <c r="AC16" s="33"/>
+      <c r="AD16" s="33"/>
+      <c r="AE16" s="33"/>
+      <c r="AF16" s="33"/>
+      <c r="AG16" s="33"/>
+      <c r="AH16" s="33"/>
+      <c r="AI16" s="33"/>
+      <c r="AJ16" s="33"/>
+      <c r="AK16" s="33"/>
+      <c r="AL16" s="33"/>
+      <c r="AM16" s="33"/>
+      <c r="AN16" s="33"/>
+      <c r="AO16" s="33"/>
+      <c r="AP16" s="33"/>
+      <c r="AQ16" s="33"/>
+      <c r="AR16" s="33"/>
+      <c r="AS16" s="33"/>
+      <c r="AT16" s="33"/>
+      <c r="AU16" s="33"/>
+      <c r="AV16" s="33"/>
+      <c r="AW16" s="33"/>
+      <c r="AX16" s="33"/>
+      <c r="AY16" s="33"/>
+      <c r="AZ16" s="33"/>
+      <c r="BA16" s="33"/>
+      <c r="BB16" s="33"/>
+      <c r="BC16" s="33"/>
+      <c r="BD16" s="33"/>
+      <c r="BE16" s="33"/>
+      <c r="BF16" s="33"/>
+      <c r="BG16" s="33"/>
+      <c r="BH16" s="33"/>
+      <c r="BI16" s="33"/>
     </row>
     <row r="17" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="38" t="s">
-        <v>85</v>
+      <c r="A17" s="46" t="s">
+        <v>83</v>
       </c>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-      <c r="S17" s="34"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="34"/>
-      <c r="V17" s="34"/>
-      <c r="W17" s="34"/>
-      <c r="X17" s="34"/>
-      <c r="Y17" s="34"/>
-      <c r="Z17" s="34"/>
-      <c r="AA17" s="34"/>
-      <c r="AB17" s="34"/>
-      <c r="AC17" s="34"/>
-      <c r="AD17" s="34"/>
-      <c r="AE17" s="34"/>
-      <c r="AF17" s="34"/>
-      <c r="AG17" s="34"/>
-      <c r="AH17" s="34"/>
-      <c r="AI17" s="34"/>
-      <c r="AJ17" s="34"/>
-      <c r="AK17" s="34"/>
-      <c r="AL17" s="34"/>
-      <c r="AM17" s="34"/>
-      <c r="AN17" s="34"/>
-      <c r="AO17" s="34"/>
-      <c r="AP17" s="34"/>
-      <c r="AQ17" s="34"/>
-      <c r="AR17" s="34"/>
-      <c r="AS17" s="34"/>
-      <c r="AT17" s="34"/>
-      <c r="AU17" s="34"/>
-      <c r="AV17" s="34"/>
-      <c r="AW17" s="34"/>
-      <c r="AX17" s="34"/>
-      <c r="AY17" s="34"/>
-      <c r="AZ17" s="34"/>
-      <c r="BA17" s="34"/>
-      <c r="BB17" s="34"/>
-      <c r="BC17" s="34"/>
-      <c r="BD17" s="34"/>
-      <c r="BE17" s="34"/>
-      <c r="BF17" s="34"/>
-      <c r="BG17" s="34"/>
-      <c r="BH17" s="34"/>
-      <c r="BI17" s="34"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="47"/>
+      <c r="L17" s="47"/>
+      <c r="M17" s="47"/>
+      <c r="N17" s="47"/>
+      <c r="O17" s="47"/>
+      <c r="P17" s="47"/>
+      <c r="Q17" s="47"/>
+      <c r="R17" s="47"/>
+      <c r="S17" s="47"/>
+      <c r="T17" s="47"/>
+      <c r="U17" s="47"/>
+      <c r="V17" s="47"/>
+      <c r="W17" s="47"/>
+      <c r="X17" s="47"/>
+      <c r="Y17" s="47"/>
+      <c r="Z17" s="47"/>
+      <c r="AA17" s="47"/>
+      <c r="AB17" s="47"/>
+      <c r="AC17" s="47"/>
+      <c r="AD17" s="47"/>
+      <c r="AE17" s="47"/>
+      <c r="AF17" s="47"/>
+      <c r="AG17" s="47"/>
+      <c r="AH17" s="47"/>
+      <c r="AI17" s="47"/>
+      <c r="AJ17" s="47"/>
+      <c r="AK17" s="47"/>
+      <c r="AL17" s="47"/>
+      <c r="AM17" s="47"/>
+      <c r="AN17" s="47"/>
+      <c r="AO17" s="47"/>
+      <c r="AP17" s="47"/>
+      <c r="AQ17" s="47"/>
+      <c r="AR17" s="47"/>
+      <c r="AS17" s="47"/>
+      <c r="AT17" s="47"/>
+      <c r="AU17" s="47"/>
+      <c r="AV17" s="47"/>
+      <c r="AW17" s="47"/>
+      <c r="AX17" s="47"/>
+      <c r="AY17" s="47"/>
+      <c r="AZ17" s="47"/>
+      <c r="BA17" s="47"/>
+      <c r="BB17" s="47"/>
+      <c r="BC17" s="47"/>
+      <c r="BD17" s="47"/>
+      <c r="BE17" s="47"/>
+      <c r="BF17" s="47"/>
+      <c r="BG17" s="47"/>
+      <c r="BH17" s="47"/>
+      <c r="BI17" s="47"/>
     </row>
     <row r="18" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="34"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="34"/>
-      <c r="S18" s="34"/>
-      <c r="T18" s="34"/>
-      <c r="U18" s="34"/>
-      <c r="V18" s="34"/>
-      <c r="W18" s="34"/>
-      <c r="X18" s="34"/>
-      <c r="Y18" s="34"/>
-      <c r="Z18" s="34"/>
-      <c r="AA18" s="34"/>
-      <c r="AB18" s="34"/>
-      <c r="AC18" s="34"/>
-      <c r="AD18" s="34"/>
-      <c r="AE18" s="34"/>
-      <c r="AF18" s="34"/>
-      <c r="AG18" s="34"/>
-      <c r="AH18" s="34"/>
-      <c r="AI18" s="34"/>
-      <c r="AJ18" s="34"/>
-      <c r="AK18" s="34"/>
-      <c r="AL18" s="34"/>
-      <c r="AM18" s="34"/>
-      <c r="AN18" s="34"/>
-      <c r="AO18" s="34"/>
-      <c r="AP18" s="34"/>
-      <c r="AQ18" s="34"/>
-      <c r="AR18" s="34"/>
-      <c r="AS18" s="34"/>
-      <c r="AT18" s="34"/>
-      <c r="AU18" s="34"/>
-      <c r="AV18" s="34"/>
-      <c r="AW18" s="34"/>
-      <c r="AX18" s="34"/>
-      <c r="AY18" s="34"/>
-      <c r="AZ18" s="34"/>
-      <c r="BA18" s="34"/>
-      <c r="BB18" s="34"/>
-      <c r="BC18" s="34"/>
-      <c r="BD18" s="34"/>
-      <c r="BE18" s="34"/>
-      <c r="BF18" s="34"/>
-      <c r="BG18" s="34"/>
-      <c r="BH18" s="34"/>
-      <c r="BI18" s="34"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="47"/>
+      <c r="M18" s="47"/>
+      <c r="N18" s="47"/>
+      <c r="O18" s="47"/>
+      <c r="P18" s="47"/>
+      <c r="Q18" s="47"/>
+      <c r="R18" s="47"/>
+      <c r="S18" s="47"/>
+      <c r="T18" s="47"/>
+      <c r="U18" s="47"/>
+      <c r="V18" s="47"/>
+      <c r="W18" s="47"/>
+      <c r="X18" s="47"/>
+      <c r="Y18" s="47"/>
+      <c r="Z18" s="47"/>
+      <c r="AA18" s="47"/>
+      <c r="AB18" s="47"/>
+      <c r="AC18" s="47"/>
+      <c r="AD18" s="47"/>
+      <c r="AE18" s="47"/>
+      <c r="AF18" s="47"/>
+      <c r="AG18" s="47"/>
+      <c r="AH18" s="47"/>
+      <c r="AI18" s="47"/>
+      <c r="AJ18" s="47"/>
+      <c r="AK18" s="47"/>
+      <c r="AL18" s="47"/>
+      <c r="AM18" s="47"/>
+      <c r="AN18" s="47"/>
+      <c r="AO18" s="47"/>
+      <c r="AP18" s="47"/>
+      <c r="AQ18" s="47"/>
+      <c r="AR18" s="47"/>
+      <c r="AS18" s="47"/>
+      <c r="AT18" s="47"/>
+      <c r="AU18" s="47"/>
+      <c r="AV18" s="47"/>
+      <c r="AW18" s="47"/>
+      <c r="AX18" s="47"/>
+      <c r="AY18" s="47"/>
+      <c r="AZ18" s="47"/>
+      <c r="BA18" s="47"/>
+      <c r="BB18" s="47"/>
+      <c r="BC18" s="47"/>
+      <c r="BD18" s="47"/>
+      <c r="BE18" s="47"/>
+      <c r="BF18" s="47"/>
+      <c r="BG18" s="47"/>
+      <c r="BH18" s="47"/>
+      <c r="BI18" s="47"/>
     </row>
     <row r="19" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="34"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="34"/>
-      <c r="U19" s="34"/>
-      <c r="V19" s="34"/>
-      <c r="W19" s="34"/>
-      <c r="X19" s="34"/>
-      <c r="Y19" s="34"/>
-      <c r="Z19" s="34"/>
-      <c r="AA19" s="34"/>
-      <c r="AB19" s="34"/>
-      <c r="AC19" s="34"/>
-      <c r="AD19" s="34"/>
-      <c r="AE19" s="34"/>
-      <c r="AF19" s="34"/>
-      <c r="AG19" s="34"/>
-      <c r="AH19" s="34"/>
-      <c r="AI19" s="34"/>
-      <c r="AJ19" s="34"/>
-      <c r="AK19" s="34"/>
-      <c r="AL19" s="34"/>
-      <c r="AM19" s="34"/>
-      <c r="AN19" s="34"/>
-      <c r="AO19" s="34"/>
-      <c r="AP19" s="34"/>
-      <c r="AQ19" s="34"/>
-      <c r="AR19" s="34"/>
-      <c r="AS19" s="34"/>
-      <c r="AT19" s="34"/>
-      <c r="AU19" s="34"/>
-      <c r="AV19" s="34"/>
-      <c r="AW19" s="34"/>
-      <c r="AX19" s="34"/>
-      <c r="AY19" s="34"/>
-      <c r="AZ19" s="34"/>
-      <c r="BA19" s="34"/>
-      <c r="BB19" s="34"/>
-      <c r="BC19" s="34"/>
-      <c r="BD19" s="34"/>
-      <c r="BE19" s="34"/>
-      <c r="BF19" s="34"/>
-      <c r="BG19" s="34"/>
-      <c r="BH19" s="34"/>
-      <c r="BI19" s="34"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="47"/>
+      <c r="Q19" s="47"/>
+      <c r="R19" s="47"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="47"/>
+      <c r="V19" s="47"/>
+      <c r="W19" s="47"/>
+      <c r="X19" s="47"/>
+      <c r="Y19" s="47"/>
+      <c r="Z19" s="47"/>
+      <c r="AA19" s="47"/>
+      <c r="AB19" s="47"/>
+      <c r="AC19" s="47"/>
+      <c r="AD19" s="47"/>
+      <c r="AE19" s="47"/>
+      <c r="AF19" s="47"/>
+      <c r="AG19" s="47"/>
+      <c r="AH19" s="47"/>
+      <c r="AI19" s="47"/>
+      <c r="AJ19" s="47"/>
+      <c r="AK19" s="47"/>
+      <c r="AL19" s="47"/>
+      <c r="AM19" s="47"/>
+      <c r="AN19" s="47"/>
+      <c r="AO19" s="47"/>
+      <c r="AP19" s="47"/>
+      <c r="AQ19" s="47"/>
+      <c r="AR19" s="47"/>
+      <c r="AS19" s="47"/>
+      <c r="AT19" s="47"/>
+      <c r="AU19" s="47"/>
+      <c r="AV19" s="47"/>
+      <c r="AW19" s="47"/>
+      <c r="AX19" s="47"/>
+      <c r="AY19" s="47"/>
+      <c r="AZ19" s="47"/>
+      <c r="BA19" s="47"/>
+      <c r="BB19" s="47"/>
+      <c r="BC19" s="47"/>
+      <c r="BD19" s="47"/>
+      <c r="BE19" s="47"/>
+      <c r="BF19" s="47"/>
+      <c r="BG19" s="47"/>
+      <c r="BH19" s="47"/>
+      <c r="BI19" s="47"/>
     </row>
     <row r="20" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="34"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="34"/>
-      <c r="V20" s="34"/>
-      <c r="W20" s="34"/>
-      <c r="X20" s="34"/>
-      <c r="Y20" s="34"/>
-      <c r="Z20" s="34"/>
-      <c r="AA20" s="34"/>
-      <c r="AB20" s="34"/>
-      <c r="AC20" s="34"/>
-      <c r="AD20" s="34"/>
-      <c r="AE20" s="34"/>
-      <c r="AF20" s="34"/>
-      <c r="AG20" s="34"/>
-      <c r="AH20" s="34"/>
-      <c r="AI20" s="34"/>
-      <c r="AJ20" s="34"/>
-      <c r="AK20" s="34"/>
-      <c r="AL20" s="34"/>
-      <c r="AM20" s="34"/>
-      <c r="AN20" s="34"/>
-      <c r="AO20" s="34"/>
-      <c r="AP20" s="34"/>
-      <c r="AQ20" s="34"/>
-      <c r="AR20" s="34"/>
-      <c r="AS20" s="34"/>
-      <c r="AT20" s="34"/>
-      <c r="AU20" s="34"/>
-      <c r="AV20" s="34"/>
-      <c r="AW20" s="34"/>
-      <c r="AX20" s="34"/>
-      <c r="AY20" s="34"/>
-      <c r="AZ20" s="34"/>
-      <c r="BA20" s="34"/>
-      <c r="BB20" s="34"/>
-      <c r="BC20" s="34"/>
-      <c r="BD20" s="34"/>
-      <c r="BE20" s="34"/>
-      <c r="BF20" s="34"/>
-      <c r="BG20" s="34"/>
-      <c r="BH20" s="34"/>
-      <c r="BI20" s="34"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="47"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="47"/>
+      <c r="N20" s="47"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="47"/>
+      <c r="Q20" s="47"/>
+      <c r="R20" s="47"/>
+      <c r="S20" s="47"/>
+      <c r="T20" s="47"/>
+      <c r="U20" s="47"/>
+      <c r="V20" s="47"/>
+      <c r="W20" s="47"/>
+      <c r="X20" s="47"/>
+      <c r="Y20" s="47"/>
+      <c r="Z20" s="47"/>
+      <c r="AA20" s="47"/>
+      <c r="AB20" s="47"/>
+      <c r="AC20" s="47"/>
+      <c r="AD20" s="47"/>
+      <c r="AE20" s="47"/>
+      <c r="AF20" s="47"/>
+      <c r="AG20" s="47"/>
+      <c r="AH20" s="47"/>
+      <c r="AI20" s="47"/>
+      <c r="AJ20" s="47"/>
+      <c r="AK20" s="47"/>
+      <c r="AL20" s="47"/>
+      <c r="AM20" s="47"/>
+      <c r="AN20" s="47"/>
+      <c r="AO20" s="47"/>
+      <c r="AP20" s="47"/>
+      <c r="AQ20" s="47"/>
+      <c r="AR20" s="47"/>
+      <c r="AS20" s="47"/>
+      <c r="AT20" s="47"/>
+      <c r="AU20" s="47"/>
+      <c r="AV20" s="47"/>
+      <c r="AW20" s="47"/>
+      <c r="AX20" s="47"/>
+      <c r="AY20" s="47"/>
+      <c r="AZ20" s="47"/>
+      <c r="BA20" s="47"/>
+      <c r="BB20" s="47"/>
+      <c r="BC20" s="47"/>
+      <c r="BD20" s="47"/>
+      <c r="BE20" s="47"/>
+      <c r="BF20" s="47"/>
+      <c r="BG20" s="47"/>
+      <c r="BH20" s="47"/>
+      <c r="BI20" s="47"/>
     </row>
     <row r="21" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="34"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="34"/>
-      <c r="S21" s="34"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="34"/>
-      <c r="V21" s="34"/>
-      <c r="W21" s="34"/>
-      <c r="X21" s="34"/>
-      <c r="Y21" s="34"/>
-      <c r="Z21" s="34"/>
-      <c r="AA21" s="34"/>
-      <c r="AB21" s="34"/>
-      <c r="AC21" s="34"/>
-      <c r="AD21" s="34"/>
-      <c r="AE21" s="34"/>
-      <c r="AF21" s="34"/>
-      <c r="AG21" s="34"/>
-      <c r="AH21" s="34"/>
-      <c r="AI21" s="34"/>
-      <c r="AJ21" s="34"/>
-      <c r="AK21" s="34"/>
-      <c r="AL21" s="34"/>
-      <c r="AM21" s="34"/>
-      <c r="AN21" s="34"/>
-      <c r="AO21" s="34"/>
-      <c r="AP21" s="34"/>
-      <c r="AQ21" s="34"/>
-      <c r="AR21" s="34"/>
-      <c r="AS21" s="34"/>
-      <c r="AT21" s="34"/>
-      <c r="AU21" s="34"/>
-      <c r="AV21" s="34"/>
-      <c r="AW21" s="34"/>
-      <c r="AX21" s="34"/>
-      <c r="AY21" s="34"/>
-      <c r="AZ21" s="34"/>
-      <c r="BA21" s="34"/>
-      <c r="BB21" s="34"/>
-      <c r="BC21" s="34"/>
-      <c r="BD21" s="34"/>
-      <c r="BE21" s="34"/>
-      <c r="BF21" s="34"/>
-      <c r="BG21" s="34"/>
-      <c r="BH21" s="34"/>
-      <c r="BI21" s="34"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="47"/>
+      <c r="N21" s="47"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="47"/>
+      <c r="Q21" s="47"/>
+      <c r="R21" s="47"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="47"/>
+      <c r="U21" s="47"/>
+      <c r="V21" s="47"/>
+      <c r="W21" s="47"/>
+      <c r="X21" s="47"/>
+      <c r="Y21" s="47"/>
+      <c r="Z21" s="47"/>
+      <c r="AA21" s="47"/>
+      <c r="AB21" s="47"/>
+      <c r="AC21" s="47"/>
+      <c r="AD21" s="47"/>
+      <c r="AE21" s="47"/>
+      <c r="AF21" s="47"/>
+      <c r="AG21" s="47"/>
+      <c r="AH21" s="47"/>
+      <c r="AI21" s="47"/>
+      <c r="AJ21" s="47"/>
+      <c r="AK21" s="47"/>
+      <c r="AL21" s="47"/>
+      <c r="AM21" s="47"/>
+      <c r="AN21" s="47"/>
+      <c r="AO21" s="47"/>
+      <c r="AP21" s="47"/>
+      <c r="AQ21" s="47"/>
+      <c r="AR21" s="47"/>
+      <c r="AS21" s="47"/>
+      <c r="AT21" s="47"/>
+      <c r="AU21" s="47"/>
+      <c r="AV21" s="47"/>
+      <c r="AW21" s="47"/>
+      <c r="AX21" s="47"/>
+      <c r="AY21" s="47"/>
+      <c r="AZ21" s="47"/>
+      <c r="BA21" s="47"/>
+      <c r="BB21" s="47"/>
+      <c r="BC21" s="47"/>
+      <c r="BD21" s="47"/>
+      <c r="BE21" s="47"/>
+      <c r="BF21" s="47"/>
+      <c r="BG21" s="47"/>
+      <c r="BH21" s="47"/>
+      <c r="BI21" s="47"/>
     </row>
     <row r="22" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="34"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="34"/>
-      <c r="R22" s="34"/>
-      <c r="S22" s="34"/>
-      <c r="T22" s="34"/>
-      <c r="U22" s="34"/>
-      <c r="V22" s="34"/>
-      <c r="W22" s="34"/>
-      <c r="X22" s="34"/>
-      <c r="Y22" s="34"/>
-      <c r="Z22" s="34"/>
-      <c r="AA22" s="34"/>
-      <c r="AB22" s="34"/>
-      <c r="AC22" s="34"/>
-      <c r="AD22" s="34"/>
-      <c r="AE22" s="34"/>
-      <c r="AF22" s="34"/>
-      <c r="AG22" s="34"/>
-      <c r="AH22" s="34"/>
-      <c r="AI22" s="34"/>
-      <c r="AJ22" s="34"/>
-      <c r="AK22" s="34"/>
-      <c r="AL22" s="34"/>
-      <c r="AM22" s="34"/>
-      <c r="AN22" s="34"/>
-      <c r="AO22" s="34"/>
-      <c r="AP22" s="34"/>
-      <c r="AQ22" s="34"/>
-      <c r="AR22" s="34"/>
-      <c r="AS22" s="34"/>
-      <c r="AT22" s="34"/>
-      <c r="AU22" s="34"/>
-      <c r="AV22" s="34"/>
-      <c r="AW22" s="34"/>
-      <c r="AX22" s="34"/>
-      <c r="AY22" s="34"/>
-      <c r="AZ22" s="34"/>
-      <c r="BA22" s="34"/>
-      <c r="BB22" s="34"/>
-      <c r="BC22" s="34"/>
-      <c r="BD22" s="34"/>
-      <c r="BE22" s="34"/>
-      <c r="BF22" s="34"/>
-      <c r="BG22" s="34"/>
-      <c r="BH22" s="34"/>
-      <c r="BI22" s="34"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="47"/>
+      <c r="M22" s="47"/>
+      <c r="N22" s="47"/>
+      <c r="O22" s="47"/>
+      <c r="P22" s="47"/>
+      <c r="Q22" s="47"/>
+      <c r="R22" s="47"/>
+      <c r="S22" s="47"/>
+      <c r="T22" s="47"/>
+      <c r="U22" s="47"/>
+      <c r="V22" s="47"/>
+      <c r="W22" s="47"/>
+      <c r="X22" s="47"/>
+      <c r="Y22" s="47"/>
+      <c r="Z22" s="47"/>
+      <c r="AA22" s="47"/>
+      <c r="AB22" s="47"/>
+      <c r="AC22" s="47"/>
+      <c r="AD22" s="47"/>
+      <c r="AE22" s="47"/>
+      <c r="AF22" s="47"/>
+      <c r="AG22" s="47"/>
+      <c r="AH22" s="47"/>
+      <c r="AI22" s="47"/>
+      <c r="AJ22" s="47"/>
+      <c r="AK22" s="47"/>
+      <c r="AL22" s="47"/>
+      <c r="AM22" s="47"/>
+      <c r="AN22" s="47"/>
+      <c r="AO22" s="47"/>
+      <c r="AP22" s="47"/>
+      <c r="AQ22" s="47"/>
+      <c r="AR22" s="47"/>
+      <c r="AS22" s="47"/>
+      <c r="AT22" s="47"/>
+      <c r="AU22" s="47"/>
+      <c r="AV22" s="47"/>
+      <c r="AW22" s="47"/>
+      <c r="AX22" s="47"/>
+      <c r="AY22" s="47"/>
+      <c r="AZ22" s="47"/>
+      <c r="BA22" s="47"/>
+      <c r="BB22" s="47"/>
+      <c r="BC22" s="47"/>
+      <c r="BD22" s="47"/>
+      <c r="BE22" s="47"/>
+      <c r="BF22" s="47"/>
+      <c r="BG22" s="47"/>
+      <c r="BH22" s="47"/>
+      <c r="BI22" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="AO12:BI12"/>
-    <mergeCell ref="A17:BI22"/>
-    <mergeCell ref="A16:BI16"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="K14:T14"/>
-    <mergeCell ref="U14:AD14"/>
-    <mergeCell ref="AE14:AN14"/>
-    <mergeCell ref="AO14:BI14"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:AA1"/>
+    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="AE1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="BD2:BI2"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="K9:T9"/>
+    <mergeCell ref="U9:AD9"/>
+    <mergeCell ref="AE9:AN9"/>
+    <mergeCell ref="AO9:BI9"/>
+    <mergeCell ref="A1:L2"/>
+    <mergeCell ref="AT1:AZ1"/>
+    <mergeCell ref="BA1:BC1"/>
+    <mergeCell ref="BD1:BI1"/>
+    <mergeCell ref="M2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="K10:T10"/>
+    <mergeCell ref="U10:AD10"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="G4:BI4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:BI5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:AC6"/>
+    <mergeCell ref="AD6:AI6"/>
+    <mergeCell ref="AJ6:BI6"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="K8:T8"/>
+    <mergeCell ref="U8:AD8"/>
+    <mergeCell ref="AE8:AN8"/>
+    <mergeCell ref="AO8:BI8"/>
     <mergeCell ref="AE10:AN10"/>
     <mergeCell ref="AO10:BI10"/>
     <mergeCell ref="A13:J13"/>
@@ -3164,44 +3183,14 @@
     <mergeCell ref="K12:T12"/>
     <mergeCell ref="U12:AD12"/>
     <mergeCell ref="AE12:AN12"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="K10:T10"/>
-    <mergeCell ref="U10:AD10"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="G4:BI4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:BI5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:AC6"/>
-    <mergeCell ref="AD6:AI6"/>
-    <mergeCell ref="AJ6:BI6"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="K8:T8"/>
-    <mergeCell ref="U8:AD8"/>
-    <mergeCell ref="AE8:AN8"/>
-    <mergeCell ref="AO8:BI8"/>
-    <mergeCell ref="BD2:BI2"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="K9:T9"/>
-    <mergeCell ref="U9:AD9"/>
-    <mergeCell ref="AE9:AN9"/>
-    <mergeCell ref="AO9:BI9"/>
-    <mergeCell ref="A1:L2"/>
-    <mergeCell ref="AT1:AZ1"/>
-    <mergeCell ref="BA1:BC1"/>
-    <mergeCell ref="BD1:BI1"/>
-    <mergeCell ref="M2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:AA1"/>
-    <mergeCell ref="AB1:AD1"/>
-    <mergeCell ref="AE1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="AO12:BI12"/>
+    <mergeCell ref="A17:BI22"/>
+    <mergeCell ref="A16:BI16"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="K14:T14"/>
+    <mergeCell ref="U14:AD14"/>
+    <mergeCell ref="AE14:AN14"/>
+    <mergeCell ref="AO14:BI14"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -3234,73 +3223,73 @@
       <c r="J1" s="35"/>
       <c r="K1" s="35"/>
       <c r="L1" s="35"/>
-      <c r="M1" s="31" t="s">
+      <c r="M1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="32" t="str">
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="36" t="str">
         <f>クラス仕様!R1</f>
         <v>商品購入</v>
       </c>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="31" t="s">
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="31"/>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="32" t="str">
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="36" t="str">
         <f>クラス仕様!AE1</f>
         <v>商品検索</v>
       </c>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="31" t="s">
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="36"/>
+      <c r="AH1" s="36"/>
+      <c r="AI1" s="36"/>
+      <c r="AJ1" s="36"/>
+      <c r="AK1" s="36"/>
+      <c r="AL1" s="36"/>
+      <c r="AM1" s="36"/>
+      <c r="AN1" s="36"/>
+      <c r="AO1" s="36"/>
+      <c r="AP1" s="36"/>
+      <c r="AQ1" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="AR1" s="31"/>
-      <c r="AS1" s="31"/>
-      <c r="AT1" s="32" t="s">
+      <c r="AR1" s="37"/>
+      <c r="AS1" s="37"/>
+      <c r="AT1" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="AU1" s="32"/>
-      <c r="AV1" s="32"/>
-      <c r="AW1" s="32"/>
-      <c r="AX1" s="32"/>
-      <c r="AY1" s="32"/>
-      <c r="AZ1" s="32"/>
-      <c r="BA1" s="31" t="s">
+      <c r="AU1" s="36"/>
+      <c r="AV1" s="36"/>
+      <c r="AW1" s="36"/>
+      <c r="AX1" s="36"/>
+      <c r="AY1" s="36"/>
+      <c r="AZ1" s="36"/>
+      <c r="BA1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="BB1" s="31"/>
-      <c r="BC1" s="31"/>
-      <c r="BD1" s="33">
+      <c r="BB1" s="37"/>
+      <c r="BC1" s="37"/>
+      <c r="BD1" s="34">
         <v>45566</v>
       </c>
-      <c r="BE1" s="33"/>
-      <c r="BF1" s="33"/>
-      <c r="BG1" s="33"/>
-      <c r="BH1" s="33"/>
-      <c r="BI1" s="33"/>
+      <c r="BE1" s="34"/>
+      <c r="BF1" s="34"/>
+      <c r="BG1" s="34"/>
+      <c r="BH1" s="34"/>
+      <c r="BI1" s="34"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -3512,70 +3501,70 @@
       <c r="J2" s="35"/>
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
-      <c r="M2" s="31" t="s">
+      <c r="M2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="36"/>
-      <c r="AA2" s="36"/>
-      <c r="AB2" s="31" t="s">
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="31"/>
-      <c r="AD2" s="31"/>
-      <c r="AE2" s="32" t="str">
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="37"/>
+      <c r="AE2" s="36" t="str">
         <f>クラス仕様!G5</f>
         <v>SearchResultServlet</v>
       </c>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="32"/>
-      <c r="AN2" s="32"/>
-      <c r="AO2" s="32"/>
-      <c r="AP2" s="32"/>
-      <c r="AQ2" s="31" t="s">
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
+      <c r="AJ2" s="36"/>
+      <c r="AK2" s="36"/>
+      <c r="AL2" s="36"/>
+      <c r="AM2" s="36"/>
+      <c r="AN2" s="36"/>
+      <c r="AO2" s="36"/>
+      <c r="AP2" s="36"/>
+      <c r="AQ2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="AR2" s="31"/>
-      <c r="AS2" s="31"/>
-      <c r="AT2" s="32" t="s">
+      <c r="AR2" s="37"/>
+      <c r="AS2" s="37"/>
+      <c r="AT2" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="AU2" s="32"/>
-      <c r="AV2" s="32"/>
-      <c r="AW2" s="32"/>
-      <c r="AX2" s="32"/>
-      <c r="AY2" s="32"/>
-      <c r="AZ2" s="32"/>
-      <c r="BA2" s="31" t="s">
+      <c r="AU2" s="36"/>
+      <c r="AV2" s="36"/>
+      <c r="AW2" s="36"/>
+      <c r="AX2" s="36"/>
+      <c r="AY2" s="36"/>
+      <c r="AZ2" s="36"/>
+      <c r="BA2" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="BB2" s="31"/>
-      <c r="BC2" s="31"/>
-      <c r="BD2" s="33">
-        <v>45568</v>
+      <c r="BB2" s="37"/>
+      <c r="BC2" s="37"/>
+      <c r="BD2" s="34">
+        <v>45587</v>
       </c>
-      <c r="BE2" s="33"/>
-      <c r="BF2" s="33"/>
-      <c r="BG2" s="33"/>
-      <c r="BH2" s="33"/>
-      <c r="BI2" s="33"/>
+      <c r="BE2" s="34"/>
+      <c r="BF2" s="34"/>
+      <c r="BG2" s="34"/>
+      <c r="BH2" s="34"/>
+      <c r="BI2" s="34"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -3775,71 +3764,71 @@
       <c r="IX2" s="1"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="38" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="38"/>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="38"/>
-      <c r="AM4" s="38"/>
-      <c r="AN4" s="38"/>
-      <c r="AO4" s="38"/>
-      <c r="AP4" s="38"/>
-      <c r="AQ4" s="38"/>
-      <c r="AR4" s="38"/>
-      <c r="AS4" s="38"/>
-      <c r="AT4" s="38"/>
-      <c r="AU4" s="38"/>
-      <c r="AV4" s="38"/>
-      <c r="AW4" s="38"/>
-      <c r="AX4" s="38"/>
-      <c r="AY4" s="38"/>
-      <c r="AZ4" s="38"/>
-      <c r="BA4" s="38"/>
-      <c r="BB4" s="38"/>
-      <c r="BC4" s="38"/>
-      <c r="BD4" s="38"/>
-      <c r="BE4" s="38"/>
-      <c r="BF4" s="38"/>
-      <c r="BG4" s="38"/>
-      <c r="BH4" s="38"/>
-      <c r="BI4" s="38"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="32"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="32"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="32"/>
+      <c r="AA4" s="32"/>
+      <c r="AB4" s="32"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="32"/>
+      <c r="AE4" s="32"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="32"/>
+      <c r="AH4" s="32"/>
+      <c r="AI4" s="32"/>
+      <c r="AJ4" s="32"/>
+      <c r="AK4" s="32"/>
+      <c r="AL4" s="32"/>
+      <c r="AM4" s="32"/>
+      <c r="AN4" s="32"/>
+      <c r="AO4" s="32"/>
+      <c r="AP4" s="32"/>
+      <c r="AQ4" s="32"/>
+      <c r="AR4" s="32"/>
+      <c r="AS4" s="32"/>
+      <c r="AT4" s="32"/>
+      <c r="AU4" s="32"/>
+      <c r="AV4" s="32"/>
+      <c r="AW4" s="32"/>
+      <c r="AX4" s="32"/>
+      <c r="AY4" s="32"/>
+      <c r="AZ4" s="32"/>
+      <c r="BA4" s="32"/>
+      <c r="BB4" s="32"/>
+      <c r="BC4" s="32"/>
+      <c r="BD4" s="32"/>
+      <c r="BE4" s="32"/>
+      <c r="BF4" s="32"/>
+      <c r="BG4" s="32"/>
+      <c r="BH4" s="32"/>
+      <c r="BI4" s="32"/>
       <c r="BJ4" s="1"/>
       <c r="BK4" s="1"/>
       <c r="BL4" s="1"/>
@@ -4039,71 +4028,71 @@
       <c r="IX4" s="1"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="38" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="38"/>
-      <c r="Y5" s="38"/>
-      <c r="Z5" s="38"/>
-      <c r="AA5" s="38"/>
-      <c r="AB5" s="38"/>
-      <c r="AC5" s="38"/>
-      <c r="AD5" s="38"/>
-      <c r="AE5" s="38"/>
-      <c r="AF5" s="38"/>
-      <c r="AG5" s="38"/>
-      <c r="AH5" s="38"/>
-      <c r="AI5" s="38"/>
-      <c r="AJ5" s="38"/>
-      <c r="AK5" s="38"/>
-      <c r="AL5" s="38"/>
-      <c r="AM5" s="38"/>
-      <c r="AN5" s="38"/>
-      <c r="AO5" s="38"/>
-      <c r="AP5" s="38"/>
-      <c r="AQ5" s="38"/>
-      <c r="AR5" s="38"/>
-      <c r="AS5" s="38"/>
-      <c r="AT5" s="38"/>
-      <c r="AU5" s="38"/>
-      <c r="AV5" s="38"/>
-      <c r="AW5" s="38"/>
-      <c r="AX5" s="38"/>
-      <c r="AY5" s="38"/>
-      <c r="AZ5" s="38"/>
-      <c r="BA5" s="38"/>
-      <c r="BB5" s="38"/>
-      <c r="BC5" s="38"/>
-      <c r="BD5" s="38"/>
-      <c r="BE5" s="38"/>
-      <c r="BF5" s="38"/>
-      <c r="BG5" s="38"/>
-      <c r="BH5" s="38"/>
-      <c r="BI5" s="38"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="32"/>
+      <c r="S5" s="32"/>
+      <c r="T5" s="32"/>
+      <c r="U5" s="32"/>
+      <c r="V5" s="32"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="32"/>
+      <c r="Z5" s="32"/>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="32"/>
+      <c r="AC5" s="32"/>
+      <c r="AD5" s="32"/>
+      <c r="AE5" s="32"/>
+      <c r="AF5" s="32"/>
+      <c r="AG5" s="32"/>
+      <c r="AH5" s="32"/>
+      <c r="AI5" s="32"/>
+      <c r="AJ5" s="32"/>
+      <c r="AK5" s="32"/>
+      <c r="AL5" s="32"/>
+      <c r="AM5" s="32"/>
+      <c r="AN5" s="32"/>
+      <c r="AO5" s="32"/>
+      <c r="AP5" s="32"/>
+      <c r="AQ5" s="32"/>
+      <c r="AR5" s="32"/>
+      <c r="AS5" s="32"/>
+      <c r="AT5" s="32"/>
+      <c r="AU5" s="32"/>
+      <c r="AV5" s="32"/>
+      <c r="AW5" s="32"/>
+      <c r="AX5" s="32"/>
+      <c r="AY5" s="32"/>
+      <c r="AZ5" s="32"/>
+      <c r="BA5" s="32"/>
+      <c r="BB5" s="32"/>
+      <c r="BC5" s="32"/>
+      <c r="BD5" s="32"/>
+      <c r="BE5" s="32"/>
+      <c r="BF5" s="32"/>
+      <c r="BG5" s="32"/>
+      <c r="BH5" s="32"/>
+      <c r="BI5" s="32"/>
       <c r="BJ5" s="1"/>
       <c r="BK5" s="1"/>
       <c r="BL5" s="1"/>
@@ -6429,9 +6418,7 @@
       <c r="IX13" s="1"/>
     </row>
     <row r="14" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -6693,7 +6680,9 @@
       <c r="IX14" s="1"/>
     </row>
     <row r="15" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
+      <c r="A15" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -6710,7 +6699,7 @@
       <c r="O15" s="10"/>
       <c r="P15" s="28"/>
       <c r="Q15" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R15" s="12"/>
       <c r="S15" s="12"/>
@@ -7755,7 +7744,7 @@
       <c r="O19" s="10"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
@@ -8279,7 +8268,7 @@
       <c r="O21" s="10"/>
       <c r="P21" s="7"/>
       <c r="Q21" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="R21" s="8"/>
       <c r="S21" s="8"/>
@@ -8524,9 +8513,7 @@
       <c r="IX21" s="1"/>
     </row>
     <row r="22" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>55</v>
-      </c>
+      <c r="A22" s="7"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -8805,7 +8792,7 @@
       <c r="O23" s="10"/>
       <c r="P23" s="28"/>
       <c r="Q23" s="30" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="R23" s="8"/>
       <c r="S23" s="8"/>
@@ -9050,7 +9037,9 @@
       <c r="IX23" s="1"/>
     </row>
     <row r="24" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
+      <c r="A24" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
@@ -9067,7 +9056,7 @@
       <c r="O24" s="10"/>
       <c r="P24" s="28"/>
       <c r="Q24" s="30" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="R24" s="8"/>
       <c r="S24" s="8"/>
@@ -9329,7 +9318,7 @@
       <c r="O25" s="10"/>
       <c r="P25" s="28"/>
       <c r="Q25" s="30" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="R25" s="8"/>
       <c r="S25" s="8"/>
@@ -9574,7 +9563,9 @@
       <c r="IX25" s="1"/>
     </row>
     <row r="26" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
+      <c r="A26" s="7" t="s">
+        <v>106</v>
+      </c>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -9591,7 +9582,7 @@
       <c r="O26" s="10"/>
       <c r="P26" s="28"/>
       <c r="Q26" s="30" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="R26" s="8"/>
       <c r="S26" s="8"/>
@@ -10617,11 +10608,29 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:O9"/>
+    <mergeCell ref="P9:AD9"/>
+    <mergeCell ref="AE9:BI9"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="P13:AS13"/>
+    <mergeCell ref="AT13:BI13"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:O10"/>
+    <mergeCell ref="P10:AD10"/>
+    <mergeCell ref="AE10:BI10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:O11"/>
+    <mergeCell ref="P11:AD11"/>
+    <mergeCell ref="AE11:BI11"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:O8"/>
+    <mergeCell ref="P8:AD8"/>
+    <mergeCell ref="AE8:BI8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:O7"/>
+    <mergeCell ref="P7:AD7"/>
+    <mergeCell ref="AE7:BI7"/>
     <mergeCell ref="BA2:BC2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="G4:BI4"/>
@@ -10638,29 +10647,11 @@
     <mergeCell ref="AT1:AZ1"/>
     <mergeCell ref="BA1:BC1"/>
     <mergeCell ref="BD1:BI1"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:O8"/>
-    <mergeCell ref="P8:AD8"/>
-    <mergeCell ref="AE8:BI8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:O7"/>
-    <mergeCell ref="P7:AD7"/>
-    <mergeCell ref="AE7:BI7"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:O9"/>
-    <mergeCell ref="P9:AD9"/>
-    <mergeCell ref="AE9:BI9"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="P13:AS13"/>
-    <mergeCell ref="AT13:BI13"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:O10"/>
-    <mergeCell ref="P10:AD10"/>
-    <mergeCell ref="AE10:BI10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:O11"/>
-    <mergeCell ref="P11:AD11"/>
-    <mergeCell ref="AE11:BI11"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <dataValidations count="1">
@@ -10677,7 +10668,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:IX61"/>
+  <dimension ref="A1:IX59"/>
   <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="2.453125" style="2"/>
@@ -10698,73 +10689,73 @@
       <c r="J1" s="35"/>
       <c r="K1" s="35"/>
       <c r="L1" s="35"/>
-      <c r="M1" s="31" t="s">
+      <c r="M1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="32" t="str">
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="36" t="str">
         <f>クラス仕様!R1</f>
         <v>商品購入</v>
       </c>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="31" t="s">
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="31"/>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="32" t="str">
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="36" t="str">
         <f>クラス仕様!AE1</f>
         <v>商品検索</v>
       </c>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="31" t="s">
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="36"/>
+      <c r="AH1" s="36"/>
+      <c r="AI1" s="36"/>
+      <c r="AJ1" s="36"/>
+      <c r="AK1" s="36"/>
+      <c r="AL1" s="36"/>
+      <c r="AM1" s="36"/>
+      <c r="AN1" s="36"/>
+      <c r="AO1" s="36"/>
+      <c r="AP1" s="36"/>
+      <c r="AQ1" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="AR1" s="31"/>
-      <c r="AS1" s="31"/>
-      <c r="AT1" s="32" t="s">
+      <c r="AR1" s="37"/>
+      <c r="AS1" s="37"/>
+      <c r="AT1" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="AU1" s="32"/>
-      <c r="AV1" s="32"/>
-      <c r="AW1" s="32"/>
-      <c r="AX1" s="32"/>
-      <c r="AY1" s="32"/>
-      <c r="AZ1" s="32"/>
-      <c r="BA1" s="31" t="s">
+      <c r="AU1" s="36"/>
+      <c r="AV1" s="36"/>
+      <c r="AW1" s="36"/>
+      <c r="AX1" s="36"/>
+      <c r="AY1" s="36"/>
+      <c r="AZ1" s="36"/>
+      <c r="BA1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="BB1" s="31"/>
-      <c r="BC1" s="31"/>
-      <c r="BD1" s="33">
+      <c r="BB1" s="37"/>
+      <c r="BC1" s="37"/>
+      <c r="BD1" s="34">
         <v>45566</v>
       </c>
-      <c r="BE1" s="33"/>
-      <c r="BF1" s="33"/>
-      <c r="BG1" s="33"/>
-      <c r="BH1" s="33"/>
-      <c r="BI1" s="33"/>
+      <c r="BE1" s="34"/>
+      <c r="BF1" s="34"/>
+      <c r="BG1" s="34"/>
+      <c r="BH1" s="34"/>
+      <c r="BI1" s="34"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -10976,70 +10967,70 @@
       <c r="J2" s="35"/>
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
-      <c r="M2" s="31" t="s">
+      <c r="M2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="36"/>
-      <c r="AA2" s="36"/>
-      <c r="AB2" s="31" t="s">
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="31"/>
-      <c r="AD2" s="31"/>
-      <c r="AE2" s="32" t="str">
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="37"/>
+      <c r="AE2" s="36" t="str">
         <f>クラス仕様!G5</f>
         <v>SearchResultServlet</v>
       </c>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="32"/>
-      <c r="AM2" s="32"/>
-      <c r="AN2" s="32"/>
-      <c r="AO2" s="32"/>
-      <c r="AP2" s="32"/>
-      <c r="AQ2" s="31" t="s">
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
+      <c r="AJ2" s="36"/>
+      <c r="AK2" s="36"/>
+      <c r="AL2" s="36"/>
+      <c r="AM2" s="36"/>
+      <c r="AN2" s="36"/>
+      <c r="AO2" s="36"/>
+      <c r="AP2" s="36"/>
+      <c r="AQ2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="AR2" s="31"/>
-      <c r="AS2" s="31"/>
-      <c r="AT2" s="32" t="s">
+      <c r="AR2" s="37"/>
+      <c r="AS2" s="37"/>
+      <c r="AT2" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="AU2" s="32"/>
-      <c r="AV2" s="32"/>
-      <c r="AW2" s="32"/>
-      <c r="AX2" s="32"/>
-      <c r="AY2" s="32"/>
-      <c r="AZ2" s="32"/>
-      <c r="BA2" s="31" t="s">
+      <c r="AU2" s="36"/>
+      <c r="AV2" s="36"/>
+      <c r="AW2" s="36"/>
+      <c r="AX2" s="36"/>
+      <c r="AY2" s="36"/>
+      <c r="AZ2" s="36"/>
+      <c r="BA2" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="BB2" s="31"/>
-      <c r="BC2" s="31"/>
-      <c r="BD2" s="33">
-        <v>45568</v>
+      <c r="BB2" s="37"/>
+      <c r="BC2" s="37"/>
+      <c r="BD2" s="34">
+        <v>45587</v>
       </c>
-      <c r="BE2" s="33"/>
-      <c r="BF2" s="33"/>
-      <c r="BG2" s="33"/>
-      <c r="BH2" s="33"/>
-      <c r="BI2" s="33"/>
+      <c r="BE2" s="34"/>
+      <c r="BF2" s="34"/>
+      <c r="BG2" s="34"/>
+      <c r="BH2" s="34"/>
+      <c r="BI2" s="34"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -11239,71 +11230,71 @@
       <c r="IX2" s="1"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="38" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="38"/>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="38"/>
-      <c r="AM4" s="38"/>
-      <c r="AN4" s="38"/>
-      <c r="AO4" s="38"/>
-      <c r="AP4" s="38"/>
-      <c r="AQ4" s="38"/>
-      <c r="AR4" s="38"/>
-      <c r="AS4" s="38"/>
-      <c r="AT4" s="38"/>
-      <c r="AU4" s="38"/>
-      <c r="AV4" s="38"/>
-      <c r="AW4" s="38"/>
-      <c r="AX4" s="38"/>
-      <c r="AY4" s="38"/>
-      <c r="AZ4" s="38"/>
-      <c r="BA4" s="38"/>
-      <c r="BB4" s="38"/>
-      <c r="BC4" s="38"/>
-      <c r="BD4" s="38"/>
-      <c r="BE4" s="38"/>
-      <c r="BF4" s="38"/>
-      <c r="BG4" s="38"/>
-      <c r="BH4" s="38"/>
-      <c r="BI4" s="38"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="32"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="32"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="32"/>
+      <c r="AA4" s="32"/>
+      <c r="AB4" s="32"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="32"/>
+      <c r="AE4" s="32"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="32"/>
+      <c r="AH4" s="32"/>
+      <c r="AI4" s="32"/>
+      <c r="AJ4" s="32"/>
+      <c r="AK4" s="32"/>
+      <c r="AL4" s="32"/>
+      <c r="AM4" s="32"/>
+      <c r="AN4" s="32"/>
+      <c r="AO4" s="32"/>
+      <c r="AP4" s="32"/>
+      <c r="AQ4" s="32"/>
+      <c r="AR4" s="32"/>
+      <c r="AS4" s="32"/>
+      <c r="AT4" s="32"/>
+      <c r="AU4" s="32"/>
+      <c r="AV4" s="32"/>
+      <c r="AW4" s="32"/>
+      <c r="AX4" s="32"/>
+      <c r="AY4" s="32"/>
+      <c r="AZ4" s="32"/>
+      <c r="BA4" s="32"/>
+      <c r="BB4" s="32"/>
+      <c r="BC4" s="32"/>
+      <c r="BD4" s="32"/>
+      <c r="BE4" s="32"/>
+      <c r="BF4" s="32"/>
+      <c r="BG4" s="32"/>
+      <c r="BH4" s="32"/>
+      <c r="BI4" s="32"/>
       <c r="BJ4" s="1"/>
       <c r="BK4" s="1"/>
       <c r="BL4" s="1"/>
@@ -11503,71 +11494,71 @@
       <c r="IX4" s="1"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="38" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="38"/>
-      <c r="Y5" s="38"/>
-      <c r="Z5" s="38"/>
-      <c r="AA5" s="38"/>
-      <c r="AB5" s="38"/>
-      <c r="AC5" s="38"/>
-      <c r="AD5" s="38"/>
-      <c r="AE5" s="38"/>
-      <c r="AF5" s="38"/>
-      <c r="AG5" s="38"/>
-      <c r="AH5" s="38"/>
-      <c r="AI5" s="38"/>
-      <c r="AJ5" s="38"/>
-      <c r="AK5" s="38"/>
-      <c r="AL5" s="38"/>
-      <c r="AM5" s="38"/>
-      <c r="AN5" s="38"/>
-      <c r="AO5" s="38"/>
-      <c r="AP5" s="38"/>
-      <c r="AQ5" s="38"/>
-      <c r="AR5" s="38"/>
-      <c r="AS5" s="38"/>
-      <c r="AT5" s="38"/>
-      <c r="AU5" s="38"/>
-      <c r="AV5" s="38"/>
-      <c r="AW5" s="38"/>
-      <c r="AX5" s="38"/>
-      <c r="AY5" s="38"/>
-      <c r="AZ5" s="38"/>
-      <c r="BA5" s="38"/>
-      <c r="BB5" s="38"/>
-      <c r="BC5" s="38"/>
-      <c r="BD5" s="38"/>
-      <c r="BE5" s="38"/>
-      <c r="BF5" s="38"/>
-      <c r="BG5" s="38"/>
-      <c r="BH5" s="38"/>
-      <c r="BI5" s="38"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="32"/>
+      <c r="S5" s="32"/>
+      <c r="T5" s="32"/>
+      <c r="U5" s="32"/>
+      <c r="V5" s="32"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="32"/>
+      <c r="Z5" s="32"/>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="32"/>
+      <c r="AC5" s="32"/>
+      <c r="AD5" s="32"/>
+      <c r="AE5" s="32"/>
+      <c r="AF5" s="32"/>
+      <c r="AG5" s="32"/>
+      <c r="AH5" s="32"/>
+      <c r="AI5" s="32"/>
+      <c r="AJ5" s="32"/>
+      <c r="AK5" s="32"/>
+      <c r="AL5" s="32"/>
+      <c r="AM5" s="32"/>
+      <c r="AN5" s="32"/>
+      <c r="AO5" s="32"/>
+      <c r="AP5" s="32"/>
+      <c r="AQ5" s="32"/>
+      <c r="AR5" s="32"/>
+      <c r="AS5" s="32"/>
+      <c r="AT5" s="32"/>
+      <c r="AU5" s="32"/>
+      <c r="AV5" s="32"/>
+      <c r="AW5" s="32"/>
+      <c r="AX5" s="32"/>
+      <c r="AY5" s="32"/>
+      <c r="AZ5" s="32"/>
+      <c r="BA5" s="32"/>
+      <c r="BB5" s="32"/>
+      <c r="BC5" s="32"/>
+      <c r="BD5" s="32"/>
+      <c r="BE5" s="32"/>
+      <c r="BF5" s="32"/>
+      <c r="BG5" s="32"/>
+      <c r="BH5" s="32"/>
+      <c r="BI5" s="32"/>
       <c r="BJ5" s="1"/>
       <c r="BK5" s="1"/>
       <c r="BL5" s="1"/>
@@ -13373,7 +13364,7 @@
       <c r="B12" s="39"/>
       <c r="C12" s="39"/>
       <c r="D12" s="40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" s="40"/>
       <c r="F12" s="40"/>
@@ -13387,7 +13378,7 @@
       <c r="N12" s="40"/>
       <c r="O12" s="40"/>
       <c r="P12" s="40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q12" s="40"/>
       <c r="R12" s="40"/>
@@ -13404,7 +13395,7 @@
       <c r="AC12" s="40"/>
       <c r="AD12" s="40"/>
       <c r="AE12" s="45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF12" s="45"/>
       <c r="AG12" s="45"/>
@@ -14161,9 +14152,7 @@
       <c r="IX14" s="1"/>
     </row>
     <row r="15" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="A15" s="4"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -14425,7 +14414,9 @@
       <c r="IX15" s="1"/>
     </row>
     <row r="16" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
+      <c r="A16" s="7" t="s">
+        <v>105</v>
+      </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -14442,7 +14433,7 @@
       <c r="O16" s="10"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R16" s="12"/>
       <c r="S16" s="12"/>
@@ -14702,7 +14693,7 @@
       <c r="N17" s="9"/>
       <c r="O17" s="10"/>
       <c r="P17" s="28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q17" s="11"/>
       <c r="R17" s="12"/>
@@ -14948,7 +14939,9 @@
       <c r="IX17" s="1"/>
     </row>
     <row r="18" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
+      <c r="A18" s="7" t="s">
+        <v>105</v>
+      </c>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -14965,7 +14958,7 @@
       <c r="O18" s="10"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="R18" s="12"/>
       <c r="S18" s="9"/>
@@ -15227,7 +15220,7 @@
       <c r="O19" s="10"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
@@ -15486,7 +15479,7 @@
       <c r="N20" s="9"/>
       <c r="O20" s="10"/>
       <c r="P20" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q20" s="11"/>
       <c r="R20" s="9"/>
@@ -15730,7 +15723,9 @@
       <c r="IX20" s="1"/>
     </row>
     <row r="21" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
+      <c r="A21" s="7" t="s">
+        <v>105</v>
+      </c>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -15747,7 +15742,7 @@
       <c r="O21" s="10"/>
       <c r="P21" s="7"/>
       <c r="Q21" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R21" s="12"/>
       <c r="S21" s="8"/>
@@ -16009,7 +16004,7 @@
       <c r="O22" s="10"/>
       <c r="P22" s="7"/>
       <c r="Q22" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R22" s="9"/>
       <c r="S22" s="8"/>
@@ -16270,7 +16265,7 @@
       <c r="N23" s="9"/>
       <c r="O23" s="10"/>
       <c r="P23" s="28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="8"/>
@@ -16533,7 +16528,7 @@
       <c r="O24" s="10"/>
       <c r="P24" s="7"/>
       <c r="Q24" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R24" s="8"/>
       <c r="S24" s="8"/>
@@ -16795,7 +16790,7 @@
       <c r="O25" s="10"/>
       <c r="P25" s="7"/>
       <c r="Q25" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R25" s="8"/>
       <c r="S25" s="8"/>
@@ -17057,7 +17052,7 @@
       <c r="O26" s="10"/>
       <c r="P26" s="7"/>
       <c r="Q26" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R26" s="8"/>
       <c r="S26" s="13"/>
@@ -17317,7 +17312,7 @@
       <c r="N27" s="9"/>
       <c r="O27" s="10"/>
       <c r="P27" s="28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="13"/>
@@ -17579,7 +17574,7 @@
       <c r="O28" s="10"/>
       <c r="P28" s="7"/>
       <c r="Q28" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R28" s="13"/>
       <c r="S28" s="8"/>
@@ -17841,7 +17836,7 @@
       <c r="O29" s="10"/>
       <c r="P29" s="7"/>
       <c r="Q29" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R29" s="13"/>
       <c r="S29" s="8"/>
@@ -18103,7 +18098,7 @@
       <c r="O30" s="10"/>
       <c r="P30" s="7"/>
       <c r="R30" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S30" s="13"/>
       <c r="T30" s="13"/>
@@ -18365,7 +18360,7 @@
       <c r="P31" s="20"/>
       <c r="R31" s="21"/>
       <c r="S31" s="13" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="T31" s="13"/>
       <c r="U31" s="13"/>
@@ -18626,7 +18621,7 @@
       <c r="P32" s="7"/>
       <c r="R32" s="9"/>
       <c r="S32" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T32" s="13"/>
       <c r="U32" s="13"/>
@@ -18887,7 +18882,7 @@
       <c r="P33" s="20"/>
       <c r="R33" s="21"/>
       <c r="S33" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T33" s="13"/>
       <c r="U33" s="13"/>
@@ -19148,7 +19143,7 @@
       <c r="P34" s="20"/>
       <c r="R34" s="21"/>
       <c r="S34" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T34" s="13"/>
       <c r="U34" s="22"/>
@@ -19409,7 +19404,7 @@
       <c r="P35" s="7"/>
       <c r="R35" s="9"/>
       <c r="S35" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="T35" s="13"/>
       <c r="U35" s="13"/>
@@ -19670,7 +19665,7 @@
       <c r="P36" s="7"/>
       <c r="R36" s="9"/>
       <c r="S36" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T36" s="13"/>
       <c r="U36" s="13"/>
@@ -19929,7 +19924,7 @@
       <c r="N37" s="9"/>
       <c r="O37" s="10"/>
       <c r="P37" s="28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="13"/>
@@ -20192,7 +20187,7 @@
       <c r="O38" s="10"/>
       <c r="P38" s="7"/>
       <c r="Q38" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R38" s="13"/>
       <c r="S38" s="13"/>
@@ -20454,7 +20449,7 @@
       <c r="O39" s="10"/>
       <c r="P39" s="7"/>
       <c r="Q39" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="R39" s="13"/>
       <c r="S39" s="13"/>
@@ -20716,7 +20711,7 @@
       <c r="O40" s="10"/>
       <c r="P40" s="7"/>
       <c r="Q40" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="R40" s="9"/>
       <c r="S40" s="13"/>
@@ -20978,7 +20973,7 @@
       <c r="O41" s="10"/>
       <c r="P41" s="3"/>
       <c r="Q41" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="R41" s="9"/>
       <c r="S41" s="13"/>
@@ -21239,7 +21234,7 @@
       <c r="N42" s="9"/>
       <c r="O42" s="10"/>
       <c r="P42" s="29" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q42" s="9"/>
       <c r="R42" s="25"/>
@@ -21501,7 +21496,7 @@
       <c r="N43" s="9"/>
       <c r="O43" s="10"/>
       <c r="P43" s="29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="25"/>
@@ -21764,7 +21759,7 @@
       <c r="O44" s="10"/>
       <c r="P44" s="3"/>
       <c r="Q44" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R44" s="13"/>
       <c r="S44" s="13"/>
@@ -22026,7 +22021,7 @@
       <c r="O45" s="10"/>
       <c r="P45" s="3"/>
       <c r="Q45" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R45" s="13"/>
       <c r="S45" s="26"/>
@@ -22288,7 +22283,7 @@
       <c r="O46" s="10"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R46" s="13"/>
       <c r="S46" s="26"/>
@@ -22550,7 +22545,7 @@
       <c r="O47" s="10"/>
       <c r="P47" s="7"/>
       <c r="Q47" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R47" s="26"/>
       <c r="S47" s="26"/>
@@ -22795,7 +22790,9 @@
       <c r="IX47" s="1"/>
     </row>
     <row r="48" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="7"/>
+      <c r="A48" s="7" t="s">
+        <v>106</v>
+      </c>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
@@ -22812,7 +22809,7 @@
       <c r="O48" s="10"/>
       <c r="P48" s="7"/>
       <c r="Q48" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="R48" s="27"/>
       <c r="S48" s="27"/>
@@ -23074,7 +23071,7 @@
       <c r="O49" s="10"/>
       <c r="P49" s="7"/>
       <c r="Q49" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R49" s="27"/>
       <c r="S49" s="27"/>
@@ -23336,7 +23333,7 @@
       <c r="O50" s="10"/>
       <c r="P50" s="23"/>
       <c r="Q50" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R50" s="27"/>
       <c r="S50" s="13"/>
@@ -23581,7 +23578,9 @@
       <c r="IX50" s="1"/>
     </row>
     <row r="51" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="7"/>
+      <c r="A51" s="7" t="s">
+        <v>105</v>
+      </c>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
@@ -23598,7 +23597,7 @@
       <c r="O51" s="10"/>
       <c r="P51" s="7"/>
       <c r="Q51" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="R51" s="27"/>
       <c r="S51" s="27"/>
@@ -23860,7 +23859,7 @@
       <c r="O52" s="10"/>
       <c r="P52" s="7"/>
       <c r="Q52" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R52" s="27"/>
       <c r="S52" s="27"/>
@@ -24122,7 +24121,7 @@
       <c r="O53" s="10"/>
       <c r="P53" s="7"/>
       <c r="R53" s="30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S53" s="27"/>
       <c r="T53" s="13"/>
@@ -24366,7 +24365,9 @@
       <c r="IX53" s="1"/>
     </row>
     <row r="54" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="7"/>
+      <c r="A54" s="7" t="s">
+        <v>105</v>
+      </c>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
@@ -24383,7 +24384,7 @@
       <c r="O54" s="10"/>
       <c r="P54" s="7"/>
       <c r="R54" s="30" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S54" s="27"/>
       <c r="T54" s="13"/>
@@ -24644,7 +24645,7 @@
       <c r="O55" s="10"/>
       <c r="P55" s="7"/>
       <c r="R55" s="30" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S55" s="27"/>
       <c r="T55" s="13"/>
@@ -24888,7 +24889,9 @@
       <c r="IX55" s="1"/>
     </row>
     <row r="56" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="7"/>
+      <c r="A56" s="7" t="s">
+        <v>106</v>
+      </c>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
@@ -24905,7 +24908,7 @@
       <c r="O56" s="10"/>
       <c r="P56" s="7"/>
       <c r="R56" s="30" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="S56" s="27"/>
       <c r="T56" s="13"/>
@@ -25164,16 +25167,14 @@
       <c r="M57" s="9"/>
       <c r="N57" s="9"/>
       <c r="O57" s="10"/>
-      <c r="P57" s="28" t="s">
-        <v>84</v>
-      </c>
+      <c r="P57" s="7"/>
       <c r="R57" s="24"/>
-      <c r="S57" s="24"/>
-      <c r="T57" s="13"/>
-      <c r="U57" s="27"/>
-      <c r="V57" s="27"/>
-      <c r="W57" s="27"/>
-      <c r="X57" s="27"/>
+      <c r="S57" s="12"/>
+      <c r="T57" s="9"/>
+      <c r="U57" s="24"/>
+      <c r="V57" s="12"/>
+      <c r="W57" s="12"/>
+      <c r="X57" s="12"/>
       <c r="Y57" s="12"/>
       <c r="Z57" s="12"/>
       <c r="AA57" s="12"/>
@@ -25195,7 +25196,7 @@
       <c r="AQ57" s="12"/>
       <c r="AR57" s="12"/>
       <c r="AS57" s="12"/>
-      <c r="AT57" s="7"/>
+      <c r="AT57" s="23"/>
       <c r="AU57" s="16"/>
       <c r="AV57" s="16"/>
       <c r="AW57" s="9"/>
@@ -25425,17 +25426,15 @@
       <c r="M58" s="9"/>
       <c r="N58" s="9"/>
       <c r="O58" s="10"/>
-      <c r="P58" s="28"/>
-      <c r="Q58" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="R58" s="24"/>
-      <c r="S58" s="24"/>
-      <c r="T58" s="13"/>
-      <c r="U58" s="27"/>
-      <c r="V58" s="27"/>
-      <c r="W58" s="27"/>
-      <c r="X58" s="27"/>
+      <c r="P58" s="7"/>
+      <c r="Q58" s="9"/>
+      <c r="R58" s="27"/>
+      <c r="S58" s="12"/>
+      <c r="T58" s="9"/>
+      <c r="U58" s="12"/>
+      <c r="V58" s="12"/>
+      <c r="W58" s="12"/>
+      <c r="X58" s="12"/>
       <c r="Y58" s="12"/>
       <c r="Z58" s="12"/>
       <c r="AA58" s="12"/>
@@ -25672,66 +25671,67 @@
       <c r="IX58" s="1"/>
     </row>
     <row r="59" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="7"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="9"/>
-      <c r="J59" s="9"/>
-      <c r="K59" s="9"/>
-      <c r="L59" s="9"/>
-      <c r="M59" s="9"/>
-      <c r="N59" s="9"/>
-      <c r="O59" s="10"/>
-      <c r="P59" s="7"/>
-      <c r="R59" s="24"/>
-      <c r="S59" s="12"/>
-      <c r="T59" s="9"/>
-      <c r="U59" s="24"/>
-      <c r="V59" s="12"/>
-      <c r="W59" s="12"/>
-      <c r="X59" s="12"/>
-      <c r="Y59" s="12"/>
-      <c r="Z59" s="12"/>
-      <c r="AA59" s="12"/>
-      <c r="AB59" s="12"/>
-      <c r="AC59" s="12"/>
-      <c r="AD59" s="12"/>
-      <c r="AE59" s="12"/>
-      <c r="AF59" s="12"/>
-      <c r="AG59" s="12"/>
-      <c r="AH59" s="12"/>
-      <c r="AI59" s="12"/>
-      <c r="AJ59" s="12"/>
-      <c r="AK59" s="12"/>
-      <c r="AL59" s="12"/>
-      <c r="AM59" s="12"/>
-      <c r="AN59" s="12"/>
-      <c r="AO59" s="12"/>
-      <c r="AP59" s="12"/>
-      <c r="AQ59" s="12"/>
-      <c r="AR59" s="12"/>
-      <c r="AS59" s="12"/>
-      <c r="AT59" s="23"/>
-      <c r="AU59" s="16"/>
-      <c r="AV59" s="16"/>
-      <c r="AW59" s="9"/>
-      <c r="AX59" s="8"/>
-      <c r="AY59" s="9"/>
-      <c r="AZ59" s="9"/>
-      <c r="BA59" s="9"/>
-      <c r="BB59" s="9"/>
-      <c r="BC59" s="9"/>
-      <c r="BD59" s="9"/>
-      <c r="BE59" s="9"/>
-      <c r="BF59" s="9"/>
-      <c r="BG59" s="9"/>
-      <c r="BH59" s="9"/>
-      <c r="BI59" s="10"/>
+      <c r="A59" s="14"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="14"/>
+      <c r="M59" s="14"/>
+      <c r="N59" s="14"/>
+      <c r="O59" s="14"/>
+      <c r="P59" s="14"/>
+      <c r="Q59" s="14"/>
+      <c r="R59" s="14"/>
+      <c r="S59" s="14"/>
+      <c r="T59" s="14"/>
+      <c r="U59" s="14"/>
+      <c r="V59" s="14"/>
+      <c r="W59" s="14"/>
+      <c r="X59" s="14"/>
+      <c r="Y59" s="14"/>
+      <c r="Z59" s="14"/>
+      <c r="AA59" s="14"/>
+      <c r="AB59" s="14"/>
+      <c r="AC59" s="14"/>
+      <c r="AD59" s="14"/>
+      <c r="AE59" s="14"/>
+      <c r="AF59" s="14"/>
+      <c r="AG59" s="14"/>
+      <c r="AH59" s="14"/>
+      <c r="AI59" s="14"/>
+      <c r="AJ59" s="14"/>
+      <c r="AK59" s="14"/>
+      <c r="AL59" s="14"/>
+      <c r="AM59" s="14"/>
+      <c r="AN59" s="14"/>
+      <c r="AO59" s="14"/>
+      <c r="AP59" s="14"/>
+      <c r="AQ59" s="14"/>
+      <c r="AR59" s="14"/>
+      <c r="AS59" s="14"/>
+      <c r="AT59" s="14"/>
+      <c r="AU59" s="14"/>
+      <c r="AV59" s="14"/>
+      <c r="AW59" s="14"/>
+      <c r="AX59" s="14"/>
+      <c r="AY59" s="14"/>
+      <c r="AZ59" s="14"/>
+      <c r="BA59" s="14"/>
+      <c r="BB59" s="14"/>
+      <c r="BC59" s="14"/>
+      <c r="BD59" s="14"/>
+      <c r="BE59" s="14"/>
+      <c r="BF59" s="14"/>
+      <c r="BG59" s="14"/>
+      <c r="BH59" s="14"/>
+      <c r="BI59" s="14"/>
       <c r="BJ59" s="1"/>
       <c r="BK59" s="1"/>
       <c r="BL59" s="1"/>
@@ -25930,538 +25930,30 @@
       <c r="IW59" s="1"/>
       <c r="IX59" s="1"/>
     </row>
-    <row r="60" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="7"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="9"/>
-      <c r="J60" s="9"/>
-      <c r="K60" s="9"/>
-      <c r="L60" s="9"/>
-      <c r="M60" s="9"/>
-      <c r="N60" s="9"/>
-      <c r="O60" s="10"/>
-      <c r="P60" s="7"/>
-      <c r="Q60" s="9"/>
-      <c r="R60" s="27"/>
-      <c r="S60" s="12"/>
-      <c r="T60" s="9"/>
-      <c r="U60" s="12"/>
-      <c r="V60" s="12"/>
-      <c r="W60" s="12"/>
-      <c r="X60" s="12"/>
-      <c r="Y60" s="12"/>
-      <c r="Z60" s="12"/>
-      <c r="AA60" s="12"/>
-      <c r="AB60" s="12"/>
-      <c r="AC60" s="12"/>
-      <c r="AD60" s="12"/>
-      <c r="AE60" s="12"/>
-      <c r="AF60" s="12"/>
-      <c r="AG60" s="12"/>
-      <c r="AH60" s="12"/>
-      <c r="AI60" s="12"/>
-      <c r="AJ60" s="12"/>
-      <c r="AK60" s="12"/>
-      <c r="AL60" s="12"/>
-      <c r="AM60" s="12"/>
-      <c r="AN60" s="12"/>
-      <c r="AO60" s="12"/>
-      <c r="AP60" s="12"/>
-      <c r="AQ60" s="12"/>
-      <c r="AR60" s="12"/>
-      <c r="AS60" s="12"/>
-      <c r="AT60" s="7"/>
-      <c r="AU60" s="16"/>
-      <c r="AV60" s="16"/>
-      <c r="AW60" s="9"/>
-      <c r="AX60" s="8"/>
-      <c r="AY60" s="9"/>
-      <c r="AZ60" s="9"/>
-      <c r="BA60" s="9"/>
-      <c r="BB60" s="9"/>
-      <c r="BC60" s="9"/>
-      <c r="BD60" s="9"/>
-      <c r="BE60" s="9"/>
-      <c r="BF60" s="9"/>
-      <c r="BG60" s="9"/>
-      <c r="BH60" s="9"/>
-      <c r="BI60" s="10"/>
-      <c r="BJ60" s="1"/>
-      <c r="BK60" s="1"/>
-      <c r="BL60" s="1"/>
-      <c r="BM60" s="1"/>
-      <c r="BN60" s="1"/>
-      <c r="BO60" s="1"/>
-      <c r="BP60" s="1"/>
-      <c r="BQ60" s="1"/>
-      <c r="BR60" s="1"/>
-      <c r="BS60" s="1"/>
-      <c r="BT60" s="1"/>
-      <c r="BU60" s="1"/>
-      <c r="BV60" s="1"/>
-      <c r="BW60" s="1"/>
-      <c r="BX60" s="1"/>
-      <c r="BY60" s="1"/>
-      <c r="BZ60" s="1"/>
-      <c r="CA60" s="1"/>
-      <c r="CB60" s="1"/>
-      <c r="CC60" s="1"/>
-      <c r="CD60" s="1"/>
-      <c r="CE60" s="1"/>
-      <c r="CF60" s="1"/>
-      <c r="CG60" s="1"/>
-      <c r="CH60" s="1"/>
-      <c r="CI60" s="1"/>
-      <c r="CJ60" s="1"/>
-      <c r="CK60" s="1"/>
-      <c r="CL60" s="1"/>
-      <c r="CM60" s="1"/>
-      <c r="CN60" s="1"/>
-      <c r="CO60" s="1"/>
-      <c r="CP60" s="1"/>
-      <c r="CQ60" s="1"/>
-      <c r="CR60" s="1"/>
-      <c r="CS60" s="1"/>
-      <c r="CT60" s="1"/>
-      <c r="CU60" s="1"/>
-      <c r="CV60" s="1"/>
-      <c r="CW60" s="1"/>
-      <c r="CX60" s="1"/>
-      <c r="CY60" s="1"/>
-      <c r="CZ60" s="1"/>
-      <c r="DA60" s="1"/>
-      <c r="DB60" s="1"/>
-      <c r="DC60" s="1"/>
-      <c r="DD60" s="1"/>
-      <c r="DE60" s="1"/>
-      <c r="DF60" s="1"/>
-      <c r="DG60" s="1"/>
-      <c r="DH60" s="1"/>
-      <c r="DI60" s="1"/>
-      <c r="DJ60" s="1"/>
-      <c r="DK60" s="1"/>
-      <c r="DL60" s="1"/>
-      <c r="DM60" s="1"/>
-      <c r="DN60" s="1"/>
-      <c r="DO60" s="1"/>
-      <c r="DP60" s="1"/>
-      <c r="DQ60" s="1"/>
-      <c r="DR60" s="1"/>
-      <c r="DS60" s="1"/>
-      <c r="DT60" s="1"/>
-      <c r="DU60" s="1"/>
-      <c r="DV60" s="1"/>
-      <c r="DW60" s="1"/>
-      <c r="DX60" s="1"/>
-      <c r="DY60" s="1"/>
-      <c r="DZ60" s="1"/>
-      <c r="EA60" s="1"/>
-      <c r="EB60" s="1"/>
-      <c r="EC60" s="1"/>
-      <c r="ED60" s="1"/>
-      <c r="EE60" s="1"/>
-      <c r="EF60" s="1"/>
-      <c r="EG60" s="1"/>
-      <c r="EH60" s="1"/>
-      <c r="EI60" s="1"/>
-      <c r="EJ60" s="1"/>
-      <c r="EK60" s="1"/>
-      <c r="EL60" s="1"/>
-      <c r="EM60" s="1"/>
-      <c r="EN60" s="1"/>
-      <c r="EO60" s="1"/>
-      <c r="EP60" s="1"/>
-      <c r="EQ60" s="1"/>
-      <c r="ER60" s="1"/>
-      <c r="ES60" s="1"/>
-      <c r="ET60" s="1"/>
-      <c r="EU60" s="1"/>
-      <c r="EV60" s="1"/>
-      <c r="EW60" s="1"/>
-      <c r="EX60" s="1"/>
-      <c r="EY60" s="1"/>
-      <c r="EZ60" s="1"/>
-      <c r="FA60" s="1"/>
-      <c r="FB60" s="1"/>
-      <c r="FC60" s="1"/>
-      <c r="FD60" s="1"/>
-      <c r="FE60" s="1"/>
-      <c r="FF60" s="1"/>
-      <c r="FG60" s="1"/>
-      <c r="FH60" s="1"/>
-      <c r="FI60" s="1"/>
-      <c r="FJ60" s="1"/>
-      <c r="FK60" s="1"/>
-      <c r="FL60" s="1"/>
-      <c r="FM60" s="1"/>
-      <c r="FN60" s="1"/>
-      <c r="FO60" s="1"/>
-      <c r="FP60" s="1"/>
-      <c r="FQ60" s="1"/>
-      <c r="FR60" s="1"/>
-      <c r="FS60" s="1"/>
-      <c r="FT60" s="1"/>
-      <c r="FU60" s="1"/>
-      <c r="FV60" s="1"/>
-      <c r="FW60" s="1"/>
-      <c r="FX60" s="1"/>
-      <c r="FY60" s="1"/>
-      <c r="FZ60" s="1"/>
-      <c r="GA60" s="1"/>
-      <c r="GB60" s="1"/>
-      <c r="GC60" s="1"/>
-      <c r="GD60" s="1"/>
-      <c r="GE60" s="1"/>
-      <c r="GF60" s="1"/>
-      <c r="GG60" s="1"/>
-      <c r="GH60" s="1"/>
-      <c r="GI60" s="1"/>
-      <c r="GJ60" s="1"/>
-      <c r="GK60" s="1"/>
-      <c r="GL60" s="1"/>
-      <c r="GM60" s="1"/>
-      <c r="GN60" s="1"/>
-      <c r="GO60" s="1"/>
-      <c r="GP60" s="1"/>
-      <c r="GQ60" s="1"/>
-      <c r="GR60" s="1"/>
-      <c r="GS60" s="1"/>
-      <c r="GT60" s="1"/>
-      <c r="GU60" s="1"/>
-      <c r="GV60" s="1"/>
-      <c r="GW60" s="1"/>
-      <c r="GX60" s="1"/>
-      <c r="GY60" s="1"/>
-      <c r="GZ60" s="1"/>
-      <c r="HA60" s="1"/>
-      <c r="HB60" s="1"/>
-      <c r="HC60" s="1"/>
-      <c r="HD60" s="1"/>
-      <c r="HE60" s="1"/>
-      <c r="HF60" s="1"/>
-      <c r="HG60" s="1"/>
-      <c r="HH60" s="1"/>
-      <c r="HI60" s="1"/>
-      <c r="HJ60" s="1"/>
-      <c r="HK60" s="1"/>
-      <c r="HL60" s="1"/>
-      <c r="HM60" s="1"/>
-      <c r="HN60" s="1"/>
-      <c r="HO60" s="1"/>
-      <c r="HP60" s="1"/>
-      <c r="HQ60" s="1"/>
-      <c r="HR60" s="1"/>
-      <c r="HS60" s="1"/>
-      <c r="HT60" s="1"/>
-      <c r="HU60" s="1"/>
-      <c r="HV60" s="1"/>
-      <c r="HW60" s="1"/>
-      <c r="HX60" s="1"/>
-      <c r="HY60" s="1"/>
-      <c r="HZ60" s="1"/>
-      <c r="IA60" s="1"/>
-      <c r="IB60" s="1"/>
-      <c r="IC60" s="1"/>
-      <c r="ID60" s="1"/>
-      <c r="IE60" s="1"/>
-      <c r="IF60" s="1"/>
-      <c r="IG60" s="1"/>
-      <c r="IH60" s="1"/>
-      <c r="II60" s="1"/>
-      <c r="IJ60" s="1"/>
-      <c r="IK60" s="1"/>
-      <c r="IL60" s="1"/>
-      <c r="IM60" s="1"/>
-      <c r="IN60" s="1"/>
-      <c r="IO60" s="1"/>
-      <c r="IP60" s="1"/>
-      <c r="IQ60" s="1"/>
-      <c r="IR60" s="1"/>
-      <c r="IS60" s="1"/>
-      <c r="IT60" s="1"/>
-      <c r="IU60" s="1"/>
-      <c r="IV60" s="1"/>
-      <c r="IW60" s="1"/>
-      <c r="IX60" s="1"/>
-    </row>
-    <row r="61" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="14"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="14"/>
-      <c r="N61" s="14"/>
-      <c r="O61" s="14"/>
-      <c r="P61" s="14"/>
-      <c r="Q61" s="14"/>
-      <c r="R61" s="14"/>
-      <c r="S61" s="14"/>
-      <c r="T61" s="14"/>
-      <c r="U61" s="14"/>
-      <c r="V61" s="14"/>
-      <c r="W61" s="14"/>
-      <c r="X61" s="14"/>
-      <c r="Y61" s="14"/>
-      <c r="Z61" s="14"/>
-      <c r="AA61" s="14"/>
-      <c r="AB61" s="14"/>
-      <c r="AC61" s="14"/>
-      <c r="AD61" s="14"/>
-      <c r="AE61" s="14"/>
-      <c r="AF61" s="14"/>
-      <c r="AG61" s="14"/>
-      <c r="AH61" s="14"/>
-      <c r="AI61" s="14"/>
-      <c r="AJ61" s="14"/>
-      <c r="AK61" s="14"/>
-      <c r="AL61" s="14"/>
-      <c r="AM61" s="14"/>
-      <c r="AN61" s="14"/>
-      <c r="AO61" s="14"/>
-      <c r="AP61" s="14"/>
-      <c r="AQ61" s="14"/>
-      <c r="AR61" s="14"/>
-      <c r="AS61" s="14"/>
-      <c r="AT61" s="14"/>
-      <c r="AU61" s="14"/>
-      <c r="AV61" s="14"/>
-      <c r="AW61" s="14"/>
-      <c r="AX61" s="14"/>
-      <c r="AY61" s="14"/>
-      <c r="AZ61" s="14"/>
-      <c r="BA61" s="14"/>
-      <c r="BB61" s="14"/>
-      <c r="BC61" s="14"/>
-      <c r="BD61" s="14"/>
-      <c r="BE61" s="14"/>
-      <c r="BF61" s="14"/>
-      <c r="BG61" s="14"/>
-      <c r="BH61" s="14"/>
-      <c r="BI61" s="14"/>
-      <c r="BJ61" s="1"/>
-      <c r="BK61" s="1"/>
-      <c r="BL61" s="1"/>
-      <c r="BM61" s="1"/>
-      <c r="BN61" s="1"/>
-      <c r="BO61" s="1"/>
-      <c r="BP61" s="1"/>
-      <c r="BQ61" s="1"/>
-      <c r="BR61" s="1"/>
-      <c r="BS61" s="1"/>
-      <c r="BT61" s="1"/>
-      <c r="BU61" s="1"/>
-      <c r="BV61" s="1"/>
-      <c r="BW61" s="1"/>
-      <c r="BX61" s="1"/>
-      <c r="BY61" s="1"/>
-      <c r="BZ61" s="1"/>
-      <c r="CA61" s="1"/>
-      <c r="CB61" s="1"/>
-      <c r="CC61" s="1"/>
-      <c r="CD61" s="1"/>
-      <c r="CE61" s="1"/>
-      <c r="CF61" s="1"/>
-      <c r="CG61" s="1"/>
-      <c r="CH61" s="1"/>
-      <c r="CI61" s="1"/>
-      <c r="CJ61" s="1"/>
-      <c r="CK61" s="1"/>
-      <c r="CL61" s="1"/>
-      <c r="CM61" s="1"/>
-      <c r="CN61" s="1"/>
-      <c r="CO61" s="1"/>
-      <c r="CP61" s="1"/>
-      <c r="CQ61" s="1"/>
-      <c r="CR61" s="1"/>
-      <c r="CS61" s="1"/>
-      <c r="CT61" s="1"/>
-      <c r="CU61" s="1"/>
-      <c r="CV61" s="1"/>
-      <c r="CW61" s="1"/>
-      <c r="CX61" s="1"/>
-      <c r="CY61" s="1"/>
-      <c r="CZ61" s="1"/>
-      <c r="DA61" s="1"/>
-      <c r="DB61" s="1"/>
-      <c r="DC61" s="1"/>
-      <c r="DD61" s="1"/>
-      <c r="DE61" s="1"/>
-      <c r="DF61" s="1"/>
-      <c r="DG61" s="1"/>
-      <c r="DH61" s="1"/>
-      <c r="DI61" s="1"/>
-      <c r="DJ61" s="1"/>
-      <c r="DK61" s="1"/>
-      <c r="DL61" s="1"/>
-      <c r="DM61" s="1"/>
-      <c r="DN61" s="1"/>
-      <c r="DO61" s="1"/>
-      <c r="DP61" s="1"/>
-      <c r="DQ61" s="1"/>
-      <c r="DR61" s="1"/>
-      <c r="DS61" s="1"/>
-      <c r="DT61" s="1"/>
-      <c r="DU61" s="1"/>
-      <c r="DV61" s="1"/>
-      <c r="DW61" s="1"/>
-      <c r="DX61" s="1"/>
-      <c r="DY61" s="1"/>
-      <c r="DZ61" s="1"/>
-      <c r="EA61" s="1"/>
-      <c r="EB61" s="1"/>
-      <c r="EC61" s="1"/>
-      <c r="ED61" s="1"/>
-      <c r="EE61" s="1"/>
-      <c r="EF61" s="1"/>
-      <c r="EG61" s="1"/>
-      <c r="EH61" s="1"/>
-      <c r="EI61" s="1"/>
-      <c r="EJ61" s="1"/>
-      <c r="EK61" s="1"/>
-      <c r="EL61" s="1"/>
-      <c r="EM61" s="1"/>
-      <c r="EN61" s="1"/>
-      <c r="EO61" s="1"/>
-      <c r="EP61" s="1"/>
-      <c r="EQ61" s="1"/>
-      <c r="ER61" s="1"/>
-      <c r="ES61" s="1"/>
-      <c r="ET61" s="1"/>
-      <c r="EU61" s="1"/>
-      <c r="EV61" s="1"/>
-      <c r="EW61" s="1"/>
-      <c r="EX61" s="1"/>
-      <c r="EY61" s="1"/>
-      <c r="EZ61" s="1"/>
-      <c r="FA61" s="1"/>
-      <c r="FB61" s="1"/>
-      <c r="FC61" s="1"/>
-      <c r="FD61" s="1"/>
-      <c r="FE61" s="1"/>
-      <c r="FF61" s="1"/>
-      <c r="FG61" s="1"/>
-      <c r="FH61" s="1"/>
-      <c r="FI61" s="1"/>
-      <c r="FJ61" s="1"/>
-      <c r="FK61" s="1"/>
-      <c r="FL61" s="1"/>
-      <c r="FM61" s="1"/>
-      <c r="FN61" s="1"/>
-      <c r="FO61" s="1"/>
-      <c r="FP61" s="1"/>
-      <c r="FQ61" s="1"/>
-      <c r="FR61" s="1"/>
-      <c r="FS61" s="1"/>
-      <c r="FT61" s="1"/>
-      <c r="FU61" s="1"/>
-      <c r="FV61" s="1"/>
-      <c r="FW61" s="1"/>
-      <c r="FX61" s="1"/>
-      <c r="FY61" s="1"/>
-      <c r="FZ61" s="1"/>
-      <c r="GA61" s="1"/>
-      <c r="GB61" s="1"/>
-      <c r="GC61" s="1"/>
-      <c r="GD61" s="1"/>
-      <c r="GE61" s="1"/>
-      <c r="GF61" s="1"/>
-      <c r="GG61" s="1"/>
-      <c r="GH61" s="1"/>
-      <c r="GI61" s="1"/>
-      <c r="GJ61" s="1"/>
-      <c r="GK61" s="1"/>
-      <c r="GL61" s="1"/>
-      <c r="GM61" s="1"/>
-      <c r="GN61" s="1"/>
-      <c r="GO61" s="1"/>
-      <c r="GP61" s="1"/>
-      <c r="GQ61" s="1"/>
-      <c r="GR61" s="1"/>
-      <c r="GS61" s="1"/>
-      <c r="GT61" s="1"/>
-      <c r="GU61" s="1"/>
-      <c r="GV61" s="1"/>
-      <c r="GW61" s="1"/>
-      <c r="GX61" s="1"/>
-      <c r="GY61" s="1"/>
-      <c r="GZ61" s="1"/>
-      <c r="HA61" s="1"/>
-      <c r="HB61" s="1"/>
-      <c r="HC61" s="1"/>
-      <c r="HD61" s="1"/>
-      <c r="HE61" s="1"/>
-      <c r="HF61" s="1"/>
-      <c r="HG61" s="1"/>
-      <c r="HH61" s="1"/>
-      <c r="HI61" s="1"/>
-      <c r="HJ61" s="1"/>
-      <c r="HK61" s="1"/>
-      <c r="HL61" s="1"/>
-      <c r="HM61" s="1"/>
-      <c r="HN61" s="1"/>
-      <c r="HO61" s="1"/>
-      <c r="HP61" s="1"/>
-      <c r="HQ61" s="1"/>
-      <c r="HR61" s="1"/>
-      <c r="HS61" s="1"/>
-      <c r="HT61" s="1"/>
-      <c r="HU61" s="1"/>
-      <c r="HV61" s="1"/>
-      <c r="HW61" s="1"/>
-      <c r="HX61" s="1"/>
-      <c r="HY61" s="1"/>
-      <c r="HZ61" s="1"/>
-      <c r="IA61" s="1"/>
-      <c r="IB61" s="1"/>
-      <c r="IC61" s="1"/>
-      <c r="ID61" s="1"/>
-      <c r="IE61" s="1"/>
-      <c r="IF61" s="1"/>
-      <c r="IG61" s="1"/>
-      <c r="IH61" s="1"/>
-      <c r="II61" s="1"/>
-      <c r="IJ61" s="1"/>
-      <c r="IK61" s="1"/>
-      <c r="IL61" s="1"/>
-      <c r="IM61" s="1"/>
-      <c r="IN61" s="1"/>
-      <c r="IO61" s="1"/>
-      <c r="IP61" s="1"/>
-      <c r="IQ61" s="1"/>
-      <c r="IR61" s="1"/>
-      <c r="IS61" s="1"/>
-      <c r="IT61" s="1"/>
-      <c r="IU61" s="1"/>
-      <c r="IV61" s="1"/>
-      <c r="IW61" s="1"/>
-      <c r="IX61" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="AE9:BI9"/>
-    <mergeCell ref="A14:O14"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:O10"/>
-    <mergeCell ref="P10:AD10"/>
-    <mergeCell ref="AE10:BI10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:O11"/>
-    <mergeCell ref="P11:AD11"/>
-    <mergeCell ref="AE11:BI11"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AE1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="AT1:AZ1"/>
+    <mergeCell ref="BA1:BC1"/>
+    <mergeCell ref="BD1:BI1"/>
+    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:O7"/>
+    <mergeCell ref="P7:AD7"/>
+    <mergeCell ref="AE7:BI7"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="G4:BI4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:BI5"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="A1:L2"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="M2:Q2"/>
     <mergeCell ref="BD2:BI2"/>
     <mergeCell ref="R1:AA1"/>
     <mergeCell ref="AB1:AD1"/>
@@ -26478,28 +25970,16 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="D9:O9"/>
     <mergeCell ref="P9:AD9"/>
-    <mergeCell ref="AT1:AZ1"/>
-    <mergeCell ref="BA1:BC1"/>
-    <mergeCell ref="BD1:BI1"/>
-    <mergeCell ref="AT2:AZ2"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:O7"/>
-    <mergeCell ref="P7:AD7"/>
-    <mergeCell ref="AE7:BI7"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="G4:BI4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:BI5"/>
-    <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="A1:L2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="M2:Q2"/>
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AE1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="AE9:BI9"/>
+    <mergeCell ref="A14:O14"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:O10"/>
+    <mergeCell ref="P10:AD10"/>
+    <mergeCell ref="AE10:BI10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:O11"/>
+    <mergeCell ref="P11:AD11"/>
+    <mergeCell ref="AE11:BI11"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
@@ -26515,9 +25995,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26653,19 +26136,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFC473E1-630C-47C0-8277-41F4549C3C72}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E88503-2BF5-4213-82B7-01925F2C7A20}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -26689,9 +26168,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E88503-2BF5-4213-82B7-01925F2C7A20}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFC473E1-630C-47C0-8277-41F4549C3C72}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>